--- a/samples/clover/design-data/xlsx/Setup.xlsx
+++ b/samples/clover/design-data/xlsx/Setup.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="977" uniqueCount="318">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="977" uniqueCount="320">
   <si>
     <t xml:space="preserve">:table Deck(key=deck_id)</t>
   </si>
@@ -883,39 +883,42 @@
     <t xml:space="preserve">foreign Tag</t>
   </si>
   <si>
+    <t xml:space="preserve">OnShopEnter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OpShopGift</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Joker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Uncommon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rare</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Negative</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Foil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Holographic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Polychrome</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OnBossDefeated</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OpAddMoney</t>
+  </si>
+  <si>
     <t xml:space="preserve">OnUse</t>
   </si>
   <si>
-    <t xml:space="preserve">OpShopGift</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Joker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Uncommon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rare</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Negative</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Foil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Holographic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Polychrome</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OnBossDefeated</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OpAddMoney</t>
-  </si>
-  <si>
     <t xml:space="preserve">OpRerollBoss</t>
   </si>
   <si>
@@ -955,13 +958,16 @@
     <t xml:space="preserve">NextShopFree</t>
   </si>
   <si>
+    <t xml:space="preserve">ThisRound</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RerollStartsFree</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OpDuplicateNextTag</t>
+  </si>
+  <si>
     <t xml:space="preserve">NextRound</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RerollStartsFree</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OpDuplicateNextTag</t>
   </si>
   <si>
     <t xml:space="preserve">OpMulMoney</t>
@@ -4692,7 +4698,7 @@
         <v>0</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>286</v>
+        <v>297</v>
       </c>
       <c r="E13" s="5" t="s">
         <v>150</v>
@@ -4719,7 +4725,7 @@
         <v>152</v>
       </c>
       <c r="AA13" s="5" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="14">
@@ -4730,7 +4736,7 @@
         <v>0</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>286</v>
+        <v>297</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>150</v>
@@ -4757,16 +4763,16 @@
         <v>152</v>
       </c>
       <c r="AA14" s="6" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AT14" s="6" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AU14" s="6">
         <v>1</v>
       </c>
       <c r="BK14" s="6" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="15">
@@ -4777,7 +4783,7 @@
         <v>0</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>286</v>
+        <v>297</v>
       </c>
       <c r="E15" s="5" t="s">
         <v>150</v>
@@ -4804,16 +4810,16 @@
         <v>152</v>
       </c>
       <c r="AA15" s="5" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AT15" s="5" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AU15" s="5">
         <v>1</v>
       </c>
       <c r="BK15" s="5" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="16">
@@ -4824,7 +4830,7 @@
         <v>0</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>286</v>
+        <v>297</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>150</v>
@@ -4851,16 +4857,16 @@
         <v>152</v>
       </c>
       <c r="AA16" s="6" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AT16" s="6" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AU16" s="6">
         <v>1</v>
       </c>
       <c r="BK16" s="6" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="17">
@@ -4871,7 +4877,7 @@
         <v>0</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>286</v>
+        <v>297</v>
       </c>
       <c r="E17" s="5" t="s">
         <v>150</v>
@@ -4898,16 +4904,16 @@
         <v>152</v>
       </c>
       <c r="AA17" s="5" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AT17" s="5" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AU17" s="5">
         <v>1</v>
       </c>
       <c r="BK17" s="5" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="18">
@@ -4918,7 +4924,7 @@
         <v>0</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>286</v>
+        <v>297</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>150</v>
@@ -4945,16 +4951,16 @@
         <v>152</v>
       </c>
       <c r="AA18" s="6" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AT18" s="6" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AU18" s="6">
         <v>1</v>
       </c>
       <c r="BK18" s="6" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="19">
@@ -4965,7 +4971,7 @@
         <v>0</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>286</v>
+        <v>297</v>
       </c>
       <c r="E19" s="5" t="s">
         <v>150</v>
@@ -4992,13 +4998,13 @@
         <v>152</v>
       </c>
       <c r="AA19" s="5" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AF19" s="5" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AG19" s="5" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AH19" s="5">
         <v>1</v>
@@ -5012,7 +5018,7 @@
         <v>0</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>286</v>
+        <v>297</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>150</v>
@@ -5039,13 +5045,13 @@
         <v>152</v>
       </c>
       <c r="AA20" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AF20" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="AG20" s="6" t="s">
         <v>308</v>
-      </c>
-      <c r="AG20" s="6" t="s">
-        <v>307</v>
       </c>
       <c r="AH20" s="6">
         <v>1</v>
@@ -5092,10 +5098,10 @@
         <v>1</v>
       </c>
       <c r="BF21" s="5" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="BH21" s="5" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="22">
@@ -5139,10 +5145,10 @@
         <v>1</v>
       </c>
       <c r="BF22" s="6" t="s">
+        <v>312</v>
+      </c>
+      <c r="BH22" s="6" t="s">
         <v>311</v>
-      </c>
-      <c r="BH22" s="6" t="s">
-        <v>310</v>
       </c>
     </row>
     <row r="23">
@@ -5153,7 +5159,7 @@
         <v>0</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>286</v>
+        <v>297</v>
       </c>
       <c r="E23" s="5" t="s">
         <v>150</v>
@@ -5180,7 +5186,7 @@
         <v>152</v>
       </c>
       <c r="AA23" s="5" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="24">
@@ -5191,7 +5197,7 @@
         <v>0</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>286</v>
+        <v>297</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>150</v>
@@ -5227,7 +5233,7 @@
         <v>178</v>
       </c>
       <c r="BH24" s="6" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
     </row>
     <row r="25">
@@ -5238,7 +5244,7 @@
         <v>0</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>286</v>
+        <v>297</v>
       </c>
       <c r="E25" s="5" t="s">
         <v>150</v>
@@ -5265,7 +5271,7 @@
         <v>152</v>
       </c>
       <c r="AA25" s="5" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="AE25" s="5">
         <v>40</v>
@@ -5282,7 +5288,7 @@
         <v>0</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>286</v>
+        <v>297</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>150</v>
@@ -5309,13 +5315,13 @@
         <v>152</v>
       </c>
       <c r="AA26" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AF26" s="6" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="AG26" s="6" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AH26" s="6">
         <v>5</v>
@@ -5329,7 +5335,7 @@
         <v>0</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>286</v>
+        <v>297</v>
       </c>
       <c r="E27" s="5" t="s">
         <v>150</v>
@@ -5356,10 +5362,10 @@
         <v>152</v>
       </c>
       <c r="AA27" s="5" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="AR27" s="5" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="AS27" s="5">
         <v>3</v>
@@ -5373,7 +5379,7 @@
         <v>0</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>286</v>
+        <v>297</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>150</v>
@@ -5400,7 +5406,7 @@
         <v>152</v>
       </c>
       <c r="AA28" s="6" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AT28" s="6" t="s">
         <v>288</v>
@@ -5409,7 +5415,7 @@
         <v>2</v>
       </c>
       <c r="AX28" s="6" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
   </sheetData>

--- a/samples/clover/design-data/xlsx/Setup.xlsx
+++ b/samples/clover/design-data/xlsx/Setup.xlsx
@@ -13,7 +13,7 @@
     <sheet name="TagEffect" sheetId="5" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1"><![CDATA[Deck!$B$2:$E$19]]></definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1"><![CDATA[Deck!$B$2:$H$19]]></definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1"><![CDATA[DeckEffect!$B$2:$BL$29]]></definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1"><![CDATA[Stake!$B$2:$H$12]]></definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1"><![CDATA[Tag!$B$2:$E$28]]></definedName>
@@ -23,12 +23,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="977" uniqueCount="320">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1031" uniqueCount="364">
   <si>
     <t xml:space="preserve">:table Deck(key=deck_id)</t>
   </si>
   <si>
-    <t xml:space="preserve">런의 시작 조건입니다. 카드 52장 자체를 바꾸는 덱과 자원을 바꾸는 덱이 갈립니다.</t>
+    <t xml:space="preserve">런의 시작 조건입니다. 카드 52장 자체를 바꾸는 덱과 자원을 바꾸는 덱이 갈립니다. 뒷면도 여기 있습니다 — 덱이 정하는 것 중 한 판 내내 보이는 유일한 것입니다.</t>
   </si>
   <si>
     <t xml:space="preserve">:field</t>
@@ -46,6 +46,15 @@
     <t xml:space="preserve">sort_order</t>
   </si>
   <si>
+    <t xml:space="preserve">back</t>
+  </si>
+  <si>
+    <t xml:space="preserve">back_ground</t>
+  </si>
+  <si>
+    <t xml:space="preserve">back_ink</t>
+  </si>
+  <si>
     <t xml:space="preserve">:type</t>
   </si>
   <si>
@@ -61,6 +70,12 @@
     <t xml:space="preserve">int (min=1, max=15)</t>
   </si>
   <si>
+    <t xml:space="preserve">CardBackKind</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string (regex="^#[0-9a-f]{6}$")</t>
+  </si>
+  <si>
     <t xml:space="preserve">:desc</t>
   </si>
   <si>
@@ -76,6 +91,15 @@
     <t xml:space="preserve">고르는 화면에서의 순서</t>
   </si>
   <si>
+    <t xml:space="preserve">뒷면의 무늬</t>
+  </si>
+  <si>
+    <t xml:space="preserve">뒷면의 바탕색</t>
+  </si>
+  <si>
+    <t xml:space="preserve">뒷면의 선 색</t>
+  </si>
+  <si>
     <t xml:space="preserve">red_deck</t>
   </si>
   <si>
@@ -85,6 +109,15 @@
     <t xml:space="preserve">처음부터</t>
   </si>
   <si>
+    <t xml:space="preserve">Classic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#f2ece0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#c0392f</t>
+  </si>
+  <si>
     <t xml:space="preserve">blue_deck</t>
   </si>
   <si>
@@ -94,6 +127,9 @@
     <t xml:space="preserve">수집 20종</t>
   </si>
   <si>
+    <t xml:space="preserve">#2f6fc0</t>
+  </si>
+  <si>
     <t xml:space="preserve">yellow_deck</t>
   </si>
   <si>
@@ -103,6 +139,12 @@
     <t xml:space="preserve">수집 50종</t>
   </si>
   <si>
+    <t xml:space="preserve">#f7f0d8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#c99a2e</t>
+  </si>
+  <si>
     <t xml:space="preserve">green_deck</t>
   </si>
   <si>
@@ -112,6 +154,12 @@
     <t xml:space="preserve">수집 75종</t>
   </si>
   <si>
+    <t xml:space="preserve">#eef2e4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#3d8b52</t>
+  </si>
+  <si>
     <t xml:space="preserve">black_deck</t>
   </si>
   <si>
@@ -121,6 +169,12 @@
     <t xml:space="preserve">수집 100종</t>
   </si>
   <si>
+    <t xml:space="preserve">#26262c</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#d8d2c4</t>
+  </si>
+  <si>
     <t xml:space="preserve">magic_deck</t>
   </si>
   <si>
@@ -130,6 +184,15 @@
     <t xml:space="preserve">붉은 덱 승리</t>
   </si>
   <si>
+    <t xml:space="preserve">Arcane</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#1e1830</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#d8b45a</t>
+  </si>
+  <si>
     <t xml:space="preserve">nebula_deck</t>
   </si>
   <si>
@@ -139,6 +202,15 @@
     <t xml:space="preserve">파란 덱 승리</t>
   </si>
   <si>
+    <t xml:space="preserve">Starfield</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#141b2e</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#8ea2f5</t>
+  </si>
+  <si>
     <t xml:space="preserve">ghost_deck</t>
   </si>
   <si>
@@ -148,6 +220,15 @@
     <t xml:space="preserve">노란 덱 승리</t>
   </si>
   <si>
+    <t xml:space="preserve">Veil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#e6ecf0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#63788d</t>
+  </si>
+  <si>
     <t xml:space="preserve">abandoned_deck</t>
   </si>
   <si>
@@ -157,6 +238,15 @@
     <t xml:space="preserve">초록 덱 승리</t>
   </si>
   <si>
+    <t xml:space="preserve">Worn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#e2d6bd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#9a5b3d</t>
+  </si>
+  <si>
     <t xml:space="preserve">checkered_deck</t>
   </si>
   <si>
@@ -166,6 +256,9 @@
     <t xml:space="preserve">검은 덱 승리</t>
   </si>
   <si>
+    <t xml:space="preserve">Checker</t>
+  </si>
+  <si>
     <t xml:space="preserve">zodiac_deck</t>
   </si>
   <si>
@@ -175,6 +268,15 @@
     <t xml:space="preserve">붉은 스테이크 승리</t>
   </si>
   <si>
+    <t xml:space="preserve">Zodiac</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#1c1830</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#e0b53b</t>
+  </si>
+  <si>
     <t xml:space="preserve">painted_deck</t>
   </si>
   <si>
@@ -184,6 +286,15 @@
     <t xml:space="preserve">초록 스테이크 승리</t>
   </si>
   <si>
+    <t xml:space="preserve">Brush</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#f4efe2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#2f8b8b</t>
+  </si>
+  <si>
     <t xml:space="preserve">anaglyph_deck</t>
   </si>
   <si>
@@ -193,6 +304,12 @@
     <t xml:space="preserve">검은 스테이크 승리</t>
   </si>
   <si>
+    <t xml:space="preserve">Anaglyph</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#d02f3a</t>
+  </si>
+  <si>
     <t xml:space="preserve">plasma_deck</t>
   </si>
   <si>
@@ -202,6 +319,15 @@
     <t xml:space="preserve">파란 스테이크 승리</t>
   </si>
   <si>
+    <t xml:space="preserve">Plasma</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#1a0f18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#ff6b9d</t>
+  </si>
+  <si>
     <t xml:space="preserve">erratic_deck</t>
   </si>
   <si>
@@ -209,6 +335,12 @@
   </si>
   <si>
     <t xml:space="preserve">주황 스테이크 승리</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Erratic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#7a4fd0</t>
   </si>
   <si>
     <t xml:space="preserve">:table DeckEffect(key="owner,order")</t>
@@ -1182,7 +1314,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr defaultColWidth="8.43" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.46875" customWidth="1"/>
@@ -1190,6 +1322,8 @@
     <col min="3" max="3" width="23.4375" customWidth="1"/>
     <col min="4" max="4" width="14.0625" customWidth="1"/>
     <col min="5" max="5" width="24.609375" customWidth="1"/>
+    <col min="6" max="6" width="16.40625" customWidth="1"/>
+    <col min="7" max="8" width="38.671875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1202,6 +1336,9 @@
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
@@ -1219,253 +1356,415 @@
       <c r="E2" s="4" t="s">
         <v>6</v>
       </c>
+      <c r="F2" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>11</v>
+        <v>14</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>16</v>
+        <v>21</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="5">
       <c r="B5" s="5" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="E5" s="5">
         <v>1</v>
       </c>
+      <c r="F5" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="6">
       <c r="B6" s="6" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="E6" s="6">
         <v>2</v>
       </c>
+      <c r="F6" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="H6" s="6" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="7">
       <c r="B7" s="5" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="E7" s="5">
         <v>3</v>
       </c>
+      <c r="F7" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="8">
       <c r="B8" s="6" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="E8" s="6">
         <v>4</v>
       </c>
+      <c r="F8" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="H8" s="6" t="s">
+        <v>44</v>
+      </c>
     </row>
     <row r="9">
       <c r="B9" s="5" t="s">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="E9" s="5">
         <v>5</v>
       </c>
+      <c r="F9" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="H9" s="5" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="10">
       <c r="B10" s="6" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="E10" s="6">
         <v>6</v>
       </c>
+      <c r="F10" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="G10" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="H10" s="6" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="11">
       <c r="B11" s="5" t="s">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>37</v>
+        <v>58</v>
       </c>
       <c r="E11" s="5">
         <v>7</v>
       </c>
+      <c r="F11" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="H11" s="5" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="12">
       <c r="B12" s="6" t="s">
-        <v>38</v>
+        <v>62</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>39</v>
+        <v>63</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>40</v>
+        <v>64</v>
       </c>
       <c r="E12" s="6">
         <v>8</v>
       </c>
+      <c r="F12" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="G12" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="H12" s="6" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="13">
       <c r="B13" s="5" t="s">
-        <v>41</v>
+        <v>68</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>42</v>
+        <v>69</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>43</v>
+        <v>70</v>
       </c>
       <c r="E13" s="5">
         <v>9</v>
       </c>
+      <c r="F13" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="H13" s="5" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="14">
       <c r="B14" s="6" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>46</v>
+        <v>76</v>
       </c>
       <c r="E14" s="6">
         <v>10</v>
       </c>
+      <c r="F14" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="G14" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="H14" s="6" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="15">
       <c r="B15" s="5" t="s">
-        <v>47</v>
+        <v>78</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>48</v>
+        <v>79</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>49</v>
+        <v>80</v>
       </c>
       <c r="E15" s="5">
         <v>11</v>
       </c>
+      <c r="F15" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="G15" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="H15" s="5" t="s">
+        <v>83</v>
+      </c>
     </row>
     <row r="16">
       <c r="B16" s="6" t="s">
-        <v>50</v>
+        <v>84</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>51</v>
+        <v>85</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>52</v>
+        <v>86</v>
       </c>
       <c r="E16" s="6">
         <v>12</v>
       </c>
+      <c r="F16" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="G16" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="H16" s="6" t="s">
+        <v>89</v>
+      </c>
     </row>
     <row r="17">
       <c r="B17" s="5" t="s">
-        <v>53</v>
+        <v>90</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>54</v>
+        <v>91</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>55</v>
+        <v>92</v>
       </c>
       <c r="E17" s="5">
         <v>13</v>
       </c>
+      <c r="F17" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="G17" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="H17" s="5" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="18">
       <c r="B18" s="6" t="s">
-        <v>56</v>
+        <v>95</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>57</v>
+        <v>96</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>58</v>
+        <v>97</v>
       </c>
       <c r="E18" s="6">
         <v>14</v>
       </c>
+      <c r="F18" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="G18" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="H18" s="6" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="19">
       <c r="B19" s="5" t="s">
-        <v>59</v>
+        <v>101</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>60</v>
+        <v>102</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>61</v>
+        <v>103</v>
       </c>
       <c r="E19" s="5">
         <v>15</v>
       </c>
+      <c r="F19" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="G19" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="H19" s="5" t="s">
+        <v>105</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="B2:E19"/>
+  <autoFilter ref="B2:H19"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1528,10 +1827,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>62</v>
+        <v>106</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>63</v>
+        <v>107</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
@@ -1601,231 +1900,231 @@
         <v>2</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>64</v>
+        <v>108</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>65</v>
+        <v>109</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>66</v>
+        <v>110</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>67</v>
+        <v>111</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>68</v>
+        <v>112</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>69</v>
+        <v>113</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>70</v>
+        <v>114</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>71</v>
+        <v>115</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>72</v>
+        <v>116</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>73</v>
+        <v>117</v>
       </c>
       <c r="L2" s="4" t="s">
-        <v>74</v>
+        <v>118</v>
       </c>
       <c r="M2" s="4" t="s">
-        <v>75</v>
+        <v>119</v>
       </c>
       <c r="N2" s="4" t="s">
-        <v>76</v>
+        <v>120</v>
       </c>
       <c r="O2" s="4" t="s">
-        <v>77</v>
+        <v>121</v>
       </c>
       <c r="P2" s="4" t="s">
-        <v>78</v>
+        <v>122</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>79</v>
+        <v>123</v>
       </c>
       <c r="R2" s="4" t="s">
-        <v>80</v>
+        <v>124</v>
       </c>
       <c r="S2" s="4" t="s">
-        <v>81</v>
+        <v>125</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>82</v>
+        <v>126</v>
       </c>
       <c r="U2" s="4" t="s">
-        <v>83</v>
+        <v>127</v>
       </c>
       <c r="V2" s="4" t="s">
-        <v>84</v>
+        <v>128</v>
       </c>
       <c r="W2" s="4" t="s">
-        <v>85</v>
+        <v>129</v>
       </c>
       <c r="X2" s="4" t="s">
-        <v>86</v>
+        <v>130</v>
       </c>
       <c r="Y2" s="4" t="s">
-        <v>87</v>
+        <v>131</v>
       </c>
       <c r="Z2" s="4" t="s">
-        <v>88</v>
+        <v>132</v>
       </c>
       <c r="AA2" s="4" t="s">
-        <v>89</v>
+        <v>133</v>
       </c>
       <c r="AB2" s="4" t="s">
-        <v>90</v>
+        <v>134</v>
       </c>
       <c r="AC2" s="4" t="s">
-        <v>91</v>
+        <v>135</v>
       </c>
       <c r="AD2" s="4" t="s">
-        <v>92</v>
+        <v>136</v>
       </c>
       <c r="AE2" s="4" t="s">
-        <v>93</v>
+        <v>137</v>
       </c>
       <c r="AF2" s="4" t="s">
-        <v>94</v>
+        <v>138</v>
       </c>
       <c r="AG2" s="4" t="s">
-        <v>95</v>
+        <v>139</v>
       </c>
       <c r="AH2" s="4" t="s">
-        <v>96</v>
+        <v>140</v>
       </c>
       <c r="AI2" s="4" t="s">
-        <v>97</v>
+        <v>141</v>
       </c>
       <c r="AJ2" s="4" t="s">
-        <v>98</v>
+        <v>142</v>
       </c>
       <c r="AK2" s="4" t="s">
-        <v>99</v>
+        <v>143</v>
       </c>
       <c r="AL2" s="4" t="s">
-        <v>100</v>
+        <v>144</v>
       </c>
       <c r="AM2" s="4" t="s">
-        <v>101</v>
+        <v>145</v>
       </c>
       <c r="AN2" s="4" t="s">
-        <v>102</v>
+        <v>146</v>
       </c>
       <c r="AO2" s="4" t="s">
-        <v>103</v>
+        <v>147</v>
       </c>
       <c r="AP2" s="4" t="s">
-        <v>104</v>
+        <v>148</v>
       </c>
       <c r="AQ2" s="4" t="s">
-        <v>105</v>
+        <v>149</v>
       </c>
       <c r="AR2" s="4" t="s">
-        <v>106</v>
+        <v>150</v>
       </c>
       <c r="AS2" s="4" t="s">
-        <v>107</v>
+        <v>151</v>
       </c>
       <c r="AT2" s="4" t="s">
-        <v>108</v>
+        <v>152</v>
       </c>
       <c r="AU2" s="4" t="s">
-        <v>109</v>
+        <v>153</v>
       </c>
       <c r="AV2" s="4" t="s">
-        <v>110</v>
+        <v>154</v>
       </c>
       <c r="AW2" s="4" t="s">
-        <v>111</v>
+        <v>155</v>
       </c>
       <c r="AX2" s="4" t="s">
-        <v>112</v>
+        <v>156</v>
       </c>
       <c r="AY2" s="4" t="s">
-        <v>113</v>
+        <v>157</v>
       </c>
       <c r="AZ2" s="4" t="s">
-        <v>114</v>
+        <v>158</v>
       </c>
       <c r="BA2" s="4" t="s">
-        <v>115</v>
+        <v>159</v>
       </c>
       <c r="BB2" s="4" t="s">
-        <v>116</v>
+        <v>160</v>
       </c>
       <c r="BC2" s="4" t="s">
-        <v>117</v>
+        <v>161</v>
       </c>
       <c r="BD2" s="4" t="s">
-        <v>118</v>
+        <v>162</v>
       </c>
       <c r="BE2" s="4" t="s">
-        <v>119</v>
+        <v>163</v>
       </c>
       <c r="BF2" s="4" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="BG2" s="4" t="s">
-        <v>121</v>
+        <v>165</v>
       </c>
       <c r="BH2" s="4" t="s">
-        <v>122</v>
+        <v>166</v>
       </c>
       <c r="BI2" s="4" t="s">
-        <v>123</v>
+        <v>167</v>
       </c>
       <c r="BJ2" s="4" t="s">
-        <v>124</v>
+        <v>168</v>
       </c>
       <c r="BK2" s="4" t="s">
-        <v>125</v>
+        <v>169</v>
       </c>
       <c r="BL2" s="4" t="s">
-        <v>126</v>
+        <v>170</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>127</v>
+        <v>171</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>128</v>
+        <v>172</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>129</v>
+        <v>173</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>130</v>
+        <v>174</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>130</v>
+        <v>174</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>131</v>
+        <v>175</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>132</v>
+        <v>176</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>133</v>
+        <v>177</v>
       </c>
       <c r="J3" s="4" t="s">
-        <v>134</v>
+        <v>178</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>130</v>
+        <v>174</v>
       </c>
       <c r="L3" s="4" t="s">
-        <v>135</v>
+        <v>179</v>
       </c>
       <c r="M3" s="4"/>
       <c r="N3" s="4"/>
@@ -1842,7 +2141,7 @@
       <c r="Y3" s="4"/>
       <c r="Z3" s="4"/>
       <c r="AA3" s="4" t="s">
-        <v>136</v>
+        <v>180</v>
       </c>
       <c r="AB3" s="4"/>
       <c r="AC3" s="4"/>
@@ -1884,40 +2183,40 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>137</v>
+        <v>181</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>138</v>
+        <v>182</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>139</v>
+        <v>183</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>140</v>
+        <v>184</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>141</v>
+        <v>185</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>142</v>
+        <v>186</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>143</v>
+        <v>187</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>144</v>
+        <v>188</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>145</v>
+        <v>189</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>146</v>
+        <v>190</v>
       </c>
       <c r="L4" s="4" t="s">
-        <v>147</v>
+        <v>191</v>
       </c>
       <c r="M4" s="4"/>
       <c r="N4" s="4"/>
@@ -1934,7 +2233,7 @@
       <c r="Y4" s="4"/>
       <c r="Z4" s="4"/>
       <c r="AA4" s="4" t="s">
-        <v>148</v>
+        <v>192</v>
       </c>
       <c r="AB4" s="4"/>
       <c r="AC4" s="4"/>
@@ -1976,1126 +2275,1126 @@
     </row>
     <row r="5">
       <c r="B5" s="5" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="C5" s="5">
         <v>0</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>149</v>
+        <v>193</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="J5" s="5" t="s">
-        <v>151</v>
+        <v>195</v>
       </c>
       <c r="K5" s="5" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="L5" s="5" t="s">
-        <v>152</v>
+        <v>196</v>
       </c>
       <c r="AA5" s="5" t="s">
-        <v>153</v>
+        <v>197</v>
       </c>
       <c r="AH5" s="5">
         <v>1</v>
       </c>
       <c r="BF5" s="5" t="s">
-        <v>154</v>
+        <v>198</v>
       </c>
     </row>
     <row r="6">
       <c r="B6" s="6" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="C6" s="6">
         <v>0</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>149</v>
+        <v>193</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="J6" s="6" t="s">
-        <v>151</v>
+        <v>195</v>
       </c>
       <c r="K6" s="6" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="L6" s="6" t="s">
-        <v>152</v>
+        <v>196</v>
       </c>
       <c r="AA6" s="6" t="s">
-        <v>153</v>
+        <v>197</v>
       </c>
       <c r="AH6" s="6">
         <v>1</v>
       </c>
       <c r="BF6" s="6" t="s">
-        <v>155</v>
+        <v>199</v>
       </c>
     </row>
     <row r="7">
       <c r="B7" s="5" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="C7" s="5">
         <v>0</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>149</v>
+        <v>193</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>151</v>
+        <v>195</v>
       </c>
       <c r="K7" s="5" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="L7" s="5" t="s">
-        <v>152</v>
+        <v>196</v>
       </c>
       <c r="AA7" s="5" t="s">
-        <v>153</v>
+        <v>197</v>
       </c>
       <c r="AH7" s="5">
         <v>10</v>
       </c>
       <c r="BF7" s="5" t="s">
-        <v>156</v>
+        <v>200</v>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="6" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="C8" s="6">
         <v>0</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>149</v>
+        <v>193</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="J8" s="6" t="s">
-        <v>151</v>
+        <v>195</v>
       </c>
       <c r="K8" s="6" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="L8" s="6" t="s">
-        <v>152</v>
+        <v>196</v>
       </c>
       <c r="AA8" s="6" t="s">
-        <v>153</v>
+        <v>197</v>
       </c>
       <c r="AH8" s="6">
         <v>1</v>
       </c>
       <c r="BF8" s="6" t="s">
-        <v>157</v>
+        <v>201</v>
       </c>
     </row>
     <row r="9">
       <c r="B9" s="5" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="C9" s="5">
         <v>1</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>149</v>
+        <v>193</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>151</v>
+        <v>195</v>
       </c>
       <c r="K9" s="5" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="L9" s="5" t="s">
-        <v>152</v>
+        <v>196</v>
       </c>
       <c r="AA9" s="5" t="s">
-        <v>153</v>
+        <v>197</v>
       </c>
       <c r="AH9" s="5">
         <v>2</v>
       </c>
       <c r="BF9" s="5" t="s">
-        <v>158</v>
+        <v>202</v>
       </c>
     </row>
     <row r="10">
       <c r="B10" s="6" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="C10" s="6">
         <v>2</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>149</v>
+        <v>193</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="J10" s="6" t="s">
-        <v>151</v>
+        <v>195</v>
       </c>
       <c r="K10" s="6" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="L10" s="6" t="s">
-        <v>152</v>
+        <v>196</v>
       </c>
       <c r="AA10" s="6" t="s">
-        <v>153</v>
+        <v>197</v>
       </c>
       <c r="AH10" s="6">
         <v>1</v>
       </c>
       <c r="BF10" s="6" t="s">
-        <v>159</v>
+        <v>203</v>
       </c>
     </row>
     <row r="11">
       <c r="B11" s="5" t="s">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="C11" s="5">
         <v>0</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>149</v>
+        <v>193</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="J11" s="5" t="s">
-        <v>151</v>
+        <v>195</v>
       </c>
       <c r="K11" s="5" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="L11" s="5" t="s">
-        <v>152</v>
+        <v>196</v>
       </c>
       <c r="AA11" s="5" t="s">
-        <v>153</v>
+        <v>197</v>
       </c>
       <c r="AH11" s="5">
         <v>1</v>
       </c>
       <c r="BF11" s="5" t="s">
-        <v>160</v>
+        <v>204</v>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="6" t="s">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="C12" s="6">
         <v>1</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>149</v>
+        <v>193</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="J12" s="6" t="s">
-        <v>151</v>
+        <v>195</v>
       </c>
       <c r="K12" s="6" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="L12" s="6" t="s">
-        <v>152</v>
+        <v>196</v>
       </c>
       <c r="AA12" s="6" t="s">
-        <v>153</v>
+        <v>197</v>
       </c>
       <c r="AH12" s="6">
         <v>-1</v>
       </c>
       <c r="BF12" s="6" t="s">
-        <v>155</v>
+        <v>199</v>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="5" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="C13" s="5">
         <v>0</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>161</v>
+        <v>205</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="J13" s="5" t="s">
-        <v>151</v>
+        <v>195</v>
       </c>
       <c r="K13" s="5" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="L13" s="5" t="s">
-        <v>152</v>
+        <v>196</v>
       </c>
       <c r="AA13" s="5" t="s">
-        <v>162</v>
+        <v>206</v>
       </c>
       <c r="AT13" s="5" t="s">
-        <v>163</v>
+        <v>207</v>
       </c>
       <c r="AU13" s="5">
         <v>1</v>
       </c>
       <c r="BK13" s="5" t="s">
-        <v>164</v>
+        <v>208</v>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="6" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="C14" s="6">
         <v>1</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>161</v>
+        <v>205</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="J14" s="6" t="s">
-        <v>151</v>
+        <v>195</v>
       </c>
       <c r="K14" s="6" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="L14" s="6" t="s">
-        <v>152</v>
+        <v>196</v>
       </c>
       <c r="AA14" s="6" t="s">
-        <v>162</v>
+        <v>206</v>
       </c>
       <c r="AT14" s="6" t="s">
-        <v>165</v>
+        <v>209</v>
       </c>
       <c r="AU14" s="6">
         <v>2</v>
       </c>
       <c r="BK14" s="6" t="s">
-        <v>166</v>
+        <v>210</v>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="5" t="s">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="C15" s="5">
         <v>0</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>161</v>
+        <v>205</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="I15" s="5" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="J15" s="5" t="s">
-        <v>151</v>
+        <v>195</v>
       </c>
       <c r="K15" s="5" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="L15" s="5" t="s">
-        <v>152</v>
+        <v>196</v>
       </c>
       <c r="AA15" s="5" t="s">
-        <v>162</v>
+        <v>206</v>
       </c>
       <c r="AT15" s="5" t="s">
-        <v>163</v>
+        <v>207</v>
       </c>
       <c r="AU15" s="5">
         <v>1</v>
       </c>
       <c r="BK15" s="5" t="s">
-        <v>167</v>
+        <v>211</v>
       </c>
     </row>
     <row r="16">
       <c r="B16" s="6" t="s">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="C16" s="6">
         <v>1</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>149</v>
+        <v>193</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="J16" s="6" t="s">
-        <v>151</v>
+        <v>195</v>
       </c>
       <c r="K16" s="6" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="L16" s="6" t="s">
-        <v>152</v>
+        <v>196</v>
       </c>
       <c r="AA16" s="6" t="s">
-        <v>153</v>
+        <v>197</v>
       </c>
       <c r="AH16" s="6">
         <v>-1</v>
       </c>
       <c r="BF16" s="6" t="s">
-        <v>168</v>
+        <v>212</v>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="5" t="s">
-        <v>38</v>
+        <v>62</v>
       </c>
       <c r="C17" s="5">
         <v>0</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>149</v>
+        <v>193</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="I17" s="5" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="J17" s="5" t="s">
-        <v>151</v>
+        <v>195</v>
       </c>
       <c r="K17" s="5" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="L17" s="5" t="s">
-        <v>152</v>
+        <v>196</v>
       </c>
       <c r="AA17" s="5" t="s">
-        <v>153</v>
+        <v>197</v>
       </c>
       <c r="AH17" s="5">
         <v>1</v>
       </c>
       <c r="BF17" s="5" t="s">
-        <v>169</v>
+        <v>213</v>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="6" t="s">
-        <v>38</v>
+        <v>62</v>
       </c>
       <c r="C18" s="6">
         <v>1</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>161</v>
+        <v>205</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="I18" s="6" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="J18" s="6" t="s">
-        <v>151</v>
+        <v>195</v>
       </c>
       <c r="K18" s="6" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="L18" s="6" t="s">
-        <v>152</v>
+        <v>196</v>
       </c>
       <c r="AA18" s="6" t="s">
-        <v>162</v>
+        <v>206</v>
       </c>
       <c r="AT18" s="6" t="s">
-        <v>170</v>
+        <v>214</v>
       </c>
       <c r="AU18" s="6">
         <v>1</v>
       </c>
       <c r="BK18" s="6" t="s">
-        <v>171</v>
+        <v>215</v>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="5" t="s">
-        <v>41</v>
+        <v>68</v>
       </c>
       <c r="C19" s="5">
         <v>0</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>149</v>
+        <v>193</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="H19" s="5" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="I19" s="5" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="J19" s="5" t="s">
-        <v>151</v>
+        <v>195</v>
       </c>
       <c r="K19" s="5" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="L19" s="5" t="s">
-        <v>152</v>
+        <v>196</v>
       </c>
       <c r="AA19" s="5" t="s">
-        <v>153</v>
+        <v>197</v>
       </c>
       <c r="AH19" s="5">
         <v>1</v>
       </c>
       <c r="BF19" s="5" t="s">
-        <v>172</v>
+        <v>216</v>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="6" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="C20" s="6">
         <v>0</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>149</v>
+        <v>193</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="I20" s="6" t="s">
-        <v>173</v>
+        <v>217</v>
       </c>
       <c r="J20" s="6" t="s">
-        <v>151</v>
+        <v>195</v>
       </c>
       <c r="K20" s="6" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="L20" s="6" t="s">
-        <v>152</v>
+        <v>196</v>
       </c>
       <c r="AA20" s="6" t="s">
-        <v>153</v>
+        <v>197</v>
       </c>
       <c r="AH20" s="6">
         <v>1</v>
       </c>
       <c r="BF20" s="6" t="s">
-        <v>174</v>
+        <v>218</v>
       </c>
     </row>
     <row r="21">
       <c r="B21" s="5" t="s">
-        <v>47</v>
+        <v>78</v>
       </c>
       <c r="C21" s="5">
         <v>0</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>161</v>
+        <v>205</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="H21" s="5" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="I21" s="5" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="J21" s="5" t="s">
-        <v>151</v>
+        <v>195</v>
       </c>
       <c r="K21" s="5" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="L21" s="5" t="s">
-        <v>152</v>
+        <v>196</v>
       </c>
       <c r="AA21" s="5" t="s">
-        <v>162</v>
+        <v>206</v>
       </c>
       <c r="AT21" s="5" t="s">
-        <v>163</v>
+        <v>207</v>
       </c>
       <c r="AU21" s="5">
         <v>1</v>
       </c>
       <c r="BK21" s="5" t="s">
-        <v>175</v>
+        <v>219</v>
       </c>
     </row>
     <row r="22">
       <c r="B22" s="6" t="s">
-        <v>47</v>
+        <v>78</v>
       </c>
       <c r="C22" s="6">
         <v>1</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>161</v>
+        <v>205</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="I22" s="6" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="J22" s="6" t="s">
-        <v>151</v>
+        <v>195</v>
       </c>
       <c r="K22" s="6" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="L22" s="6" t="s">
-        <v>152</v>
+        <v>196</v>
       </c>
       <c r="AA22" s="6" t="s">
-        <v>162</v>
+        <v>206</v>
       </c>
       <c r="AT22" s="6" t="s">
-        <v>163</v>
+        <v>207</v>
       </c>
       <c r="AU22" s="6">
         <v>1</v>
       </c>
       <c r="BK22" s="6" t="s">
-        <v>176</v>
+        <v>220</v>
       </c>
     </row>
     <row r="23">
       <c r="B23" s="5" t="s">
-        <v>47</v>
+        <v>78</v>
       </c>
       <c r="C23" s="5">
         <v>2</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>161</v>
+        <v>205</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="H23" s="5" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="I23" s="5" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="J23" s="5" t="s">
-        <v>151</v>
+        <v>195</v>
       </c>
       <c r="K23" s="5" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="L23" s="5" t="s">
-        <v>152</v>
+        <v>196</v>
       </c>
       <c r="AA23" s="5" t="s">
-        <v>162</v>
+        <v>206</v>
       </c>
       <c r="AT23" s="5" t="s">
-        <v>163</v>
+        <v>207</v>
       </c>
       <c r="AU23" s="5">
         <v>1</v>
       </c>
       <c r="BK23" s="5" t="s">
-        <v>177</v>
+        <v>221</v>
       </c>
     </row>
     <row r="24">
       <c r="B24" s="6" t="s">
-        <v>50</v>
+        <v>84</v>
       </c>
       <c r="C24" s="6">
         <v>0</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>149</v>
+        <v>193</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="I24" s="6" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="J24" s="6" t="s">
-        <v>151</v>
+        <v>195</v>
       </c>
       <c r="K24" s="6" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="L24" s="6" t="s">
-        <v>152</v>
+        <v>196</v>
       </c>
       <c r="AA24" s="6" t="s">
-        <v>153</v>
+        <v>197</v>
       </c>
       <c r="AH24" s="6">
         <v>2</v>
       </c>
       <c r="BF24" s="6" t="s">
-        <v>178</v>
+        <v>222</v>
       </c>
     </row>
     <row r="25">
       <c r="B25" s="5" t="s">
-        <v>50</v>
+        <v>84</v>
       </c>
       <c r="C25" s="5">
         <v>1</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>149</v>
+        <v>193</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="H25" s="5" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="I25" s="5" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="J25" s="5" t="s">
-        <v>151</v>
+        <v>195</v>
       </c>
       <c r="K25" s="5" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="L25" s="5" t="s">
-        <v>152</v>
+        <v>196</v>
       </c>
       <c r="AA25" s="5" t="s">
-        <v>153</v>
+        <v>197</v>
       </c>
       <c r="AH25" s="5">
         <v>-1</v>
       </c>
       <c r="BF25" s="5" t="s">
-        <v>160</v>
+        <v>204</v>
       </c>
     </row>
     <row r="26">
       <c r="B26" s="6" t="s">
-        <v>53</v>
+        <v>90</v>
       </c>
       <c r="C26" s="6">
         <v>0</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>149</v>
+        <v>193</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="F26" s="6" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="I26" s="6" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="J26" s="6" t="s">
-        <v>151</v>
+        <v>195</v>
       </c>
       <c r="K26" s="6" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="L26" s="6" t="s">
-        <v>152</v>
+        <v>196</v>
       </c>
       <c r="AA26" s="6" t="s">
-        <v>153</v>
+        <v>197</v>
       </c>
       <c r="AH26" s="6">
         <v>1</v>
       </c>
       <c r="BF26" s="6" t="s">
-        <v>179</v>
+        <v>223</v>
       </c>
     </row>
     <row r="27">
       <c r="B27" s="5" t="s">
-        <v>56</v>
+        <v>95</v>
       </c>
       <c r="C27" s="5">
         <v>0</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>149</v>
+        <v>193</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="H27" s="5" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="I27" s="5" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="J27" s="5" t="s">
-        <v>151</v>
+        <v>195</v>
       </c>
       <c r="K27" s="5" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="L27" s="5" t="s">
-        <v>152</v>
+        <v>196</v>
       </c>
       <c r="AA27" s="5" t="s">
-        <v>153</v>
+        <v>197</v>
       </c>
       <c r="AH27" s="5">
         <v>1</v>
       </c>
       <c r="BF27" s="5" t="s">
-        <v>180</v>
+        <v>224</v>
       </c>
     </row>
     <row r="28">
       <c r="B28" s="6" t="s">
-        <v>56</v>
+        <v>95</v>
       </c>
       <c r="C28" s="6">
         <v>1</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>149</v>
+        <v>193</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="F28" s="6" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="I28" s="6" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="J28" s="6" t="s">
-        <v>151</v>
+        <v>195</v>
       </c>
       <c r="K28" s="6" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="L28" s="6" t="s">
-        <v>152</v>
+        <v>196</v>
       </c>
       <c r="AA28" s="6" t="s">
-        <v>153</v>
+        <v>197</v>
       </c>
       <c r="AH28" s="6">
         <v>20000</v>
       </c>
       <c r="BF28" s="6" t="s">
-        <v>181</v>
+        <v>225</v>
       </c>
       <c r="BG28" s="6" t="s">
-        <v>182</v>
+        <v>226</v>
       </c>
     </row>
     <row r="29">
       <c r="B29" s="5" t="s">
-        <v>59</v>
+        <v>101</v>
       </c>
       <c r="C29" s="5">
         <v>0</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>149</v>
+        <v>193</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="H29" s="5" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="I29" s="5" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="J29" s="5" t="s">
-        <v>151</v>
+        <v>195</v>
       </c>
       <c r="K29" s="5" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="L29" s="5" t="s">
-        <v>152</v>
+        <v>196</v>
       </c>
       <c r="AA29" s="5" t="s">
-        <v>153</v>
+        <v>197</v>
       </c>
       <c r="AH29" s="5">
         <v>1</v>
       </c>
       <c r="BF29" s="5" t="s">
-        <v>183</v>
+        <v>227</v>
       </c>
     </row>
   </sheetData>
@@ -3120,10 +3419,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>184</v>
+        <v>228</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>185</v>
+        <v>229</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
@@ -3137,85 +3436,85 @@
         <v>2</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>186</v>
+        <v>230</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>4</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>187</v>
+        <v>231</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>188</v>
+        <v>232</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>189</v>
+        <v>233</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>190</v>
+        <v>234</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>191</v>
+        <v>235</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>192</v>
+        <v>236</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>193</v>
+        <v>237</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>194</v>
+        <v>238</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>195</v>
+        <v>239</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>196</v>
+        <v>240</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>197</v>
+        <v>241</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>198</v>
+        <v>242</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>199</v>
+        <v>243</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>200</v>
+        <v>244</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>201</v>
+        <v>245</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>202</v>
+        <v>246</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>203</v>
+        <v>247</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>204</v>
+        <v>248</v>
       </c>
     </row>
     <row r="5">
       <c r="B5" s="5" t="s">
-        <v>205</v>
+        <v>249</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>206</v>
+        <v>250</v>
       </c>
       <c r="D5" s="5">
         <v>1</v>
@@ -3227,7 +3526,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>207</v>
+        <v>251</v>
       </c>
       <c r="H5" s="5">
         <v>0</v>
@@ -3235,10 +3534,10 @@
     </row>
     <row r="6">
       <c r="B6" s="6" t="s">
-        <v>208</v>
+        <v>252</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>209</v>
+        <v>253</v>
       </c>
       <c r="D6" s="6">
         <v>1</v>
@@ -3250,7 +3549,7 @@
         <v>0</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>207</v>
+        <v>251</v>
       </c>
       <c r="H6" s="6">
         <v>0</v>
@@ -3258,10 +3557,10 @@
     </row>
     <row r="7">
       <c r="B7" s="5" t="s">
-        <v>210</v>
+        <v>254</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>211</v>
+        <v>255</v>
       </c>
       <c r="D7" s="5">
         <v>2</v>
@@ -3273,7 +3572,7 @@
         <v>0</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>207</v>
+        <v>251</v>
       </c>
       <c r="H7" s="5">
         <v>0</v>
@@ -3281,10 +3580,10 @@
     </row>
     <row r="8">
       <c r="B8" s="6" t="s">
-        <v>212</v>
+        <v>256</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>213</v>
+        <v>257</v>
       </c>
       <c r="D8" s="6">
         <v>2</v>
@@ -3296,7 +3595,7 @@
         <v>0</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>214</v>
+        <v>258</v>
       </c>
       <c r="H8" s="6">
         <v>30</v>
@@ -3304,10 +3603,10 @@
     </row>
     <row r="9">
       <c r="B9" s="5" t="s">
-        <v>215</v>
+        <v>259</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>216</v>
+        <v>260</v>
       </c>
       <c r="D9" s="5">
         <v>2</v>
@@ -3319,7 +3618,7 @@
         <v>-1</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>214</v>
+        <v>258</v>
       </c>
       <c r="H9" s="5">
         <v>30</v>
@@ -3327,10 +3626,10 @@
     </row>
     <row r="10">
       <c r="B10" s="6" t="s">
-        <v>217</v>
+        <v>261</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>218</v>
+        <v>262</v>
       </c>
       <c r="D10" s="6">
         <v>3</v>
@@ -3342,7 +3641,7 @@
         <v>-1</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>214</v>
+        <v>258</v>
       </c>
       <c r="H10" s="6">
         <v>30</v>
@@ -3350,10 +3649,10 @@
     </row>
     <row r="11">
       <c r="B11" s="5" t="s">
-        <v>219</v>
+        <v>263</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>220</v>
+        <v>264</v>
       </c>
       <c r="D11" s="5">
         <v>3</v>
@@ -3365,7 +3664,7 @@
         <v>-1</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>221</v>
+        <v>265</v>
       </c>
       <c r="H11" s="5">
         <v>30</v>
@@ -3373,10 +3672,10 @@
     </row>
     <row r="12">
       <c r="B12" s="6" t="s">
-        <v>222</v>
+        <v>266</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>223</v>
+        <v>267</v>
       </c>
       <c r="D12" s="6">
         <v>3</v>
@@ -3388,7 +3687,7 @@
         <v>-1</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>224</v>
+        <v>268</v>
       </c>
       <c r="H12" s="6">
         <v>30</v>
@@ -3414,10 +3713,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>225</v>
+        <v>269</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>226</v>
+        <v>270</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
@@ -3428,13 +3727,13 @@
         <v>2</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>227</v>
+        <v>271</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>4</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>228</v>
+        <v>272</v>
       </c>
       <c r="E2" s="4" t="s">
         <v>6</v>
@@ -3442,44 +3741,44 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>229</v>
+        <v>273</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>230</v>
+        <v>274</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>231</v>
+        <v>275</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>232</v>
+        <v>276</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>233</v>
+        <v>277</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>234</v>
+        <v>278</v>
       </c>
     </row>
     <row r="5">
       <c r="B5" s="5" t="s">
-        <v>235</v>
+        <v>279</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>236</v>
+        <v>280</v>
       </c>
       <c r="D5" s="5">
         <v>1</v>
@@ -3490,10 +3789,10 @@
     </row>
     <row r="6">
       <c r="B6" s="6" t="s">
-        <v>237</v>
+        <v>281</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>238</v>
+        <v>282</v>
       </c>
       <c r="D6" s="6">
         <v>1</v>
@@ -3504,10 +3803,10 @@
     </row>
     <row r="7">
       <c r="B7" s="5" t="s">
-        <v>239</v>
+        <v>283</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>240</v>
+        <v>284</v>
       </c>
       <c r="D7" s="5">
         <v>2</v>
@@ -3518,10 +3817,10 @@
     </row>
     <row r="8">
       <c r="B8" s="6" t="s">
-        <v>241</v>
+        <v>285</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>242</v>
+        <v>286</v>
       </c>
       <c r="D8" s="6">
         <v>1</v>
@@ -3532,10 +3831,10 @@
     </row>
     <row r="9">
       <c r="B9" s="5" t="s">
-        <v>243</v>
+        <v>287</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>244</v>
+        <v>288</v>
       </c>
       <c r="D9" s="5">
         <v>1</v>
@@ -3546,10 +3845,10 @@
     </row>
     <row r="10">
       <c r="B10" s="6" t="s">
-        <v>245</v>
+        <v>289</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>246</v>
+        <v>290</v>
       </c>
       <c r="D10" s="6">
         <v>1</v>
@@ -3560,10 +3859,10 @@
     </row>
     <row r="11">
       <c r="B11" s="5" t="s">
-        <v>247</v>
+        <v>291</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>248</v>
+        <v>292</v>
       </c>
       <c r="D11" s="5">
         <v>1</v>
@@ -3574,10 +3873,10 @@
     </row>
     <row r="12">
       <c r="B12" s="6" t="s">
-        <v>249</v>
+        <v>293</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>250</v>
+        <v>294</v>
       </c>
       <c r="D12" s="6">
         <v>1</v>
@@ -3588,10 +3887,10 @@
     </row>
     <row r="13">
       <c r="B13" s="5" t="s">
-        <v>251</v>
+        <v>295</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>252</v>
+        <v>296</v>
       </c>
       <c r="D13" s="5">
         <v>1</v>
@@ -3602,10 +3901,10 @@
     </row>
     <row r="14">
       <c r="B14" s="6" t="s">
-        <v>253</v>
+        <v>297</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>254</v>
+        <v>298</v>
       </c>
       <c r="D14" s="6">
         <v>2</v>
@@ -3616,10 +3915,10 @@
     </row>
     <row r="15">
       <c r="B15" s="5" t="s">
-        <v>255</v>
+        <v>299</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>256</v>
+        <v>300</v>
       </c>
       <c r="D15" s="5">
         <v>1</v>
@@ -3630,10 +3929,10 @@
     </row>
     <row r="16">
       <c r="B16" s="6" t="s">
-        <v>257</v>
+        <v>301</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>258</v>
+        <v>302</v>
       </c>
       <c r="D16" s="6">
         <v>2</v>
@@ -3644,10 +3943,10 @@
     </row>
     <row r="17">
       <c r="B17" s="5" t="s">
-        <v>259</v>
+        <v>303</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>260</v>
+        <v>304</v>
       </c>
       <c r="D17" s="5">
         <v>2</v>
@@ -3658,10 +3957,10 @@
     </row>
     <row r="18">
       <c r="B18" s="6" t="s">
-        <v>261</v>
+        <v>305</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>262</v>
+        <v>306</v>
       </c>
       <c r="D18" s="6">
         <v>2</v>
@@ -3672,10 +3971,10 @@
     </row>
     <row r="19">
       <c r="B19" s="5" t="s">
-        <v>263</v>
+        <v>307</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>264</v>
+        <v>308</v>
       </c>
       <c r="D19" s="5">
         <v>2</v>
@@ -3686,10 +3985,10 @@
     </row>
     <row r="20">
       <c r="B20" s="6" t="s">
-        <v>265</v>
+        <v>309</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>266</v>
+        <v>310</v>
       </c>
       <c r="D20" s="6">
         <v>2</v>
@@ -3700,10 +3999,10 @@
     </row>
     <row r="21">
       <c r="B21" s="5" t="s">
-        <v>267</v>
+        <v>311</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>268</v>
+        <v>312</v>
       </c>
       <c r="D21" s="5">
         <v>1</v>
@@ -3714,10 +4013,10 @@
     </row>
     <row r="22">
       <c r="B22" s="6" t="s">
-        <v>269</v>
+        <v>313</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>270</v>
+        <v>314</v>
       </c>
       <c r="D22" s="6">
         <v>1</v>
@@ -3728,10 +4027,10 @@
     </row>
     <row r="23">
       <c r="B23" s="5" t="s">
-        <v>271</v>
+        <v>315</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>272</v>
+        <v>316</v>
       </c>
       <c r="D23" s="5">
         <v>1</v>
@@ -3742,10 +4041,10 @@
     </row>
     <row r="24">
       <c r="B24" s="6" t="s">
-        <v>273</v>
+        <v>317</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>274</v>
+        <v>318</v>
       </c>
       <c r="D24" s="6">
         <v>1</v>
@@ -3756,10 +4055,10 @@
     </row>
     <row r="25">
       <c r="B25" s="5" t="s">
-        <v>275</v>
+        <v>319</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>276</v>
+        <v>320</v>
       </c>
       <c r="D25" s="5">
         <v>1</v>
@@ -3770,10 +4069,10 @@
     </row>
     <row r="26">
       <c r="B26" s="6" t="s">
-        <v>277</v>
+        <v>321</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>278</v>
+        <v>322</v>
       </c>
       <c r="D26" s="6">
         <v>1</v>
@@ -3784,10 +4083,10 @@
     </row>
     <row r="27">
       <c r="B27" s="5" t="s">
-        <v>279</v>
+        <v>323</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>280</v>
+        <v>324</v>
       </c>
       <c r="D27" s="5">
         <v>2</v>
@@ -3798,10 +4097,10 @@
     </row>
     <row r="28">
       <c r="B28" s="6" t="s">
-        <v>281</v>
+        <v>325</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>282</v>
+        <v>326</v>
       </c>
       <c r="D28" s="6">
         <v>2</v>
@@ -3877,10 +4176,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>283</v>
+        <v>327</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>284</v>
+        <v>328</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
@@ -3950,231 +4249,231 @@
         <v>2</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>64</v>
+        <v>108</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>65</v>
+        <v>109</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>66</v>
+        <v>110</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>67</v>
+        <v>111</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>68</v>
+        <v>112</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>69</v>
+        <v>113</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>70</v>
+        <v>114</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>71</v>
+        <v>115</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>72</v>
+        <v>116</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>73</v>
+        <v>117</v>
       </c>
       <c r="L2" s="4" t="s">
-        <v>74</v>
+        <v>118</v>
       </c>
       <c r="M2" s="4" t="s">
-        <v>75</v>
+        <v>119</v>
       </c>
       <c r="N2" s="4" t="s">
-        <v>76</v>
+        <v>120</v>
       </c>
       <c r="O2" s="4" t="s">
-        <v>77</v>
+        <v>121</v>
       </c>
       <c r="P2" s="4" t="s">
-        <v>78</v>
+        <v>122</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>79</v>
+        <v>123</v>
       </c>
       <c r="R2" s="4" t="s">
-        <v>80</v>
+        <v>124</v>
       </c>
       <c r="S2" s="4" t="s">
-        <v>81</v>
+        <v>125</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>82</v>
+        <v>126</v>
       </c>
       <c r="U2" s="4" t="s">
-        <v>83</v>
+        <v>127</v>
       </c>
       <c r="V2" s="4" t="s">
-        <v>84</v>
+        <v>128</v>
       </c>
       <c r="W2" s="4" t="s">
-        <v>85</v>
+        <v>129</v>
       </c>
       <c r="X2" s="4" t="s">
-        <v>86</v>
+        <v>130</v>
       </c>
       <c r="Y2" s="4" t="s">
-        <v>87</v>
+        <v>131</v>
       </c>
       <c r="Z2" s="4" t="s">
-        <v>88</v>
+        <v>132</v>
       </c>
       <c r="AA2" s="4" t="s">
-        <v>89</v>
+        <v>133</v>
       </c>
       <c r="AB2" s="4" t="s">
-        <v>90</v>
+        <v>134</v>
       </c>
       <c r="AC2" s="4" t="s">
-        <v>91</v>
+        <v>135</v>
       </c>
       <c r="AD2" s="4" t="s">
-        <v>92</v>
+        <v>136</v>
       </c>
       <c r="AE2" s="4" t="s">
-        <v>93</v>
+        <v>137</v>
       </c>
       <c r="AF2" s="4" t="s">
-        <v>94</v>
+        <v>138</v>
       </c>
       <c r="AG2" s="4" t="s">
-        <v>95</v>
+        <v>139</v>
       </c>
       <c r="AH2" s="4" t="s">
-        <v>96</v>
+        <v>140</v>
       </c>
       <c r="AI2" s="4" t="s">
-        <v>97</v>
+        <v>141</v>
       </c>
       <c r="AJ2" s="4" t="s">
-        <v>98</v>
+        <v>142</v>
       </c>
       <c r="AK2" s="4" t="s">
-        <v>99</v>
+        <v>143</v>
       </c>
       <c r="AL2" s="4" t="s">
-        <v>100</v>
+        <v>144</v>
       </c>
       <c r="AM2" s="4" t="s">
-        <v>101</v>
+        <v>145</v>
       </c>
       <c r="AN2" s="4" t="s">
-        <v>102</v>
+        <v>146</v>
       </c>
       <c r="AO2" s="4" t="s">
-        <v>103</v>
+        <v>147</v>
       </c>
       <c r="AP2" s="4" t="s">
-        <v>104</v>
+        <v>148</v>
       </c>
       <c r="AQ2" s="4" t="s">
-        <v>105</v>
+        <v>149</v>
       </c>
       <c r="AR2" s="4" t="s">
-        <v>106</v>
+        <v>150</v>
       </c>
       <c r="AS2" s="4" t="s">
-        <v>107</v>
+        <v>151</v>
       </c>
       <c r="AT2" s="4" t="s">
-        <v>108</v>
+        <v>152</v>
       </c>
       <c r="AU2" s="4" t="s">
-        <v>109</v>
+        <v>153</v>
       </c>
       <c r="AV2" s="4" t="s">
-        <v>110</v>
+        <v>154</v>
       </c>
       <c r="AW2" s="4" t="s">
-        <v>111</v>
+        <v>155</v>
       </c>
       <c r="AX2" s="4" t="s">
-        <v>112</v>
+        <v>156</v>
       </c>
       <c r="AY2" s="4" t="s">
-        <v>113</v>
+        <v>157</v>
       </c>
       <c r="AZ2" s="4" t="s">
-        <v>114</v>
+        <v>158</v>
       </c>
       <c r="BA2" s="4" t="s">
-        <v>115</v>
+        <v>159</v>
       </c>
       <c r="BB2" s="4" t="s">
-        <v>116</v>
+        <v>160</v>
       </c>
       <c r="BC2" s="4" t="s">
-        <v>117</v>
+        <v>161</v>
       </c>
       <c r="BD2" s="4" t="s">
-        <v>118</v>
+        <v>162</v>
       </c>
       <c r="BE2" s="4" t="s">
-        <v>119</v>
+        <v>163</v>
       </c>
       <c r="BF2" s="4" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="BG2" s="4" t="s">
-        <v>121</v>
+        <v>165</v>
       </c>
       <c r="BH2" s="4" t="s">
-        <v>122</v>
+        <v>166</v>
       </c>
       <c r="BI2" s="4" t="s">
-        <v>123</v>
+        <v>167</v>
       </c>
       <c r="BJ2" s="4" t="s">
-        <v>124</v>
+        <v>168</v>
       </c>
       <c r="BK2" s="4" t="s">
-        <v>125</v>
+        <v>169</v>
       </c>
       <c r="BL2" s="4" t="s">
-        <v>126</v>
+        <v>170</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>285</v>
+        <v>329</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>128</v>
+        <v>172</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>129</v>
+        <v>173</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>130</v>
+        <v>174</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>130</v>
+        <v>174</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>131</v>
+        <v>175</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>132</v>
+        <v>176</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>133</v>
+        <v>177</v>
       </c>
       <c r="J3" s="4" t="s">
-        <v>134</v>
+        <v>178</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>130</v>
+        <v>174</v>
       </c>
       <c r="L3" s="4" t="s">
-        <v>135</v>
+        <v>179</v>
       </c>
       <c r="M3" s="4"/>
       <c r="N3" s="4"/>
@@ -4191,7 +4490,7 @@
       <c r="Y3" s="4"/>
       <c r="Z3" s="4"/>
       <c r="AA3" s="4" t="s">
-        <v>136</v>
+        <v>180</v>
       </c>
       <c r="AB3" s="4"/>
       <c r="AC3" s="4"/>
@@ -4233,40 +4532,40 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>137</v>
+        <v>181</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>138</v>
+        <v>182</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>139</v>
+        <v>183</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>140</v>
+        <v>184</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>141</v>
+        <v>185</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>142</v>
+        <v>186</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>143</v>
+        <v>187</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>144</v>
+        <v>188</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>145</v>
+        <v>189</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>146</v>
+        <v>190</v>
       </c>
       <c r="L4" s="4" t="s">
-        <v>147</v>
+        <v>191</v>
       </c>
       <c r="M4" s="4"/>
       <c r="N4" s="4"/>
@@ -4283,7 +4582,7 @@
       <c r="Y4" s="4"/>
       <c r="Z4" s="4"/>
       <c r="AA4" s="4" t="s">
-        <v>148</v>
+        <v>192</v>
       </c>
       <c r="AB4" s="4"/>
       <c r="AC4" s="4"/>
@@ -4325,322 +4624,322 @@
     </row>
     <row r="5">
       <c r="B5" s="5" t="s">
-        <v>235</v>
+        <v>279</v>
       </c>
       <c r="C5" s="5">
         <v>0</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>286</v>
+        <v>330</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="J5" s="5" t="s">
-        <v>151</v>
+        <v>195</v>
       </c>
       <c r="K5" s="5" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="L5" s="5" t="s">
-        <v>152</v>
+        <v>196</v>
       </c>
       <c r="AA5" s="5" t="s">
-        <v>287</v>
+        <v>331</v>
       </c>
       <c r="AT5" s="5" t="s">
-        <v>288</v>
+        <v>332</v>
       </c>
       <c r="AX5" s="5" t="s">
-        <v>289</v>
+        <v>333</v>
       </c>
       <c r="BI5" s="5" t="s">
-        <v>182</v>
+        <v>226</v>
       </c>
     </row>
     <row r="6">
       <c r="B6" s="6" t="s">
-        <v>237</v>
+        <v>281</v>
       </c>
       <c r="C6" s="6">
         <v>0</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>286</v>
+        <v>330</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="J6" s="6" t="s">
-        <v>151</v>
+        <v>195</v>
       </c>
       <c r="K6" s="6" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="L6" s="6" t="s">
-        <v>152</v>
+        <v>196</v>
       </c>
       <c r="AA6" s="6" t="s">
-        <v>287</v>
+        <v>331</v>
       </c>
       <c r="AT6" s="6" t="s">
-        <v>288</v>
+        <v>332</v>
       </c>
       <c r="AX6" s="6" t="s">
-        <v>290</v>
+        <v>334</v>
       </c>
       <c r="BI6" s="6" t="s">
-        <v>182</v>
+        <v>226</v>
       </c>
     </row>
     <row r="7">
       <c r="B7" s="5" t="s">
-        <v>239</v>
+        <v>283</v>
       </c>
       <c r="C7" s="5">
         <v>0</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>286</v>
+        <v>330</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>151</v>
+        <v>195</v>
       </c>
       <c r="K7" s="5" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="L7" s="5" t="s">
-        <v>152</v>
+        <v>196</v>
       </c>
       <c r="AA7" s="5" t="s">
-        <v>287</v>
+        <v>331</v>
       </c>
       <c r="AT7" s="5" t="s">
-        <v>288</v>
+        <v>332</v>
       </c>
       <c r="AW7" s="5" t="s">
-        <v>291</v>
+        <v>335</v>
       </c>
       <c r="BI7" s="5" t="s">
-        <v>182</v>
+        <v>226</v>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="6" t="s">
-        <v>241</v>
+        <v>285</v>
       </c>
       <c r="C8" s="6">
         <v>0</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>286</v>
+        <v>330</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="J8" s="6" t="s">
-        <v>151</v>
+        <v>195</v>
       </c>
       <c r="K8" s="6" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="L8" s="6" t="s">
-        <v>152</v>
+        <v>196</v>
       </c>
       <c r="AA8" s="6" t="s">
-        <v>287</v>
+        <v>331</v>
       </c>
       <c r="AT8" s="6" t="s">
-        <v>288</v>
+        <v>332</v>
       </c>
       <c r="AW8" s="6" t="s">
-        <v>292</v>
+        <v>336</v>
       </c>
       <c r="BI8" s="6" t="s">
-        <v>182</v>
+        <v>226</v>
       </c>
     </row>
     <row r="9">
       <c r="B9" s="5" t="s">
-        <v>243</v>
+        <v>287</v>
       </c>
       <c r="C9" s="5">
         <v>0</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>286</v>
+        <v>330</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>151</v>
+        <v>195</v>
       </c>
       <c r="K9" s="5" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="L9" s="5" t="s">
-        <v>152</v>
+        <v>196</v>
       </c>
       <c r="AA9" s="5" t="s">
-        <v>287</v>
+        <v>331</v>
       </c>
       <c r="AT9" s="5" t="s">
-        <v>288</v>
+        <v>332</v>
       </c>
       <c r="AW9" s="5" t="s">
-        <v>293</v>
+        <v>337</v>
       </c>
       <c r="BI9" s="5" t="s">
-        <v>182</v>
+        <v>226</v>
       </c>
     </row>
     <row r="10">
       <c r="B10" s="6" t="s">
-        <v>245</v>
+        <v>289</v>
       </c>
       <c r="C10" s="6">
         <v>0</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>286</v>
+        <v>330</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="J10" s="6" t="s">
-        <v>151</v>
+        <v>195</v>
       </c>
       <c r="K10" s="6" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="L10" s="6" t="s">
-        <v>152</v>
+        <v>196</v>
       </c>
       <c r="AA10" s="6" t="s">
-        <v>287</v>
+        <v>331</v>
       </c>
       <c r="AT10" s="6" t="s">
-        <v>288</v>
+        <v>332</v>
       </c>
       <c r="AW10" s="6" t="s">
-        <v>294</v>
+        <v>338</v>
       </c>
       <c r="BI10" s="6" t="s">
-        <v>182</v>
+        <v>226</v>
       </c>
     </row>
     <row r="11">
       <c r="B11" s="5" t="s">
-        <v>247</v>
+        <v>291</v>
       </c>
       <c r="C11" s="5">
         <v>0</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>295</v>
+        <v>339</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="J11" s="5" t="s">
-        <v>151</v>
+        <v>195</v>
       </c>
       <c r="K11" s="5" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="L11" s="5" t="s">
-        <v>152</v>
+        <v>196</v>
       </c>
       <c r="AA11" s="5" t="s">
-        <v>296</v>
+        <v>340</v>
       </c>
       <c r="AD11" s="5">
         <v>25</v>
@@ -4648,43 +4947,43 @@
     </row>
     <row r="12">
       <c r="B12" s="6" t="s">
-        <v>249</v>
+        <v>293</v>
       </c>
       <c r="C12" s="6">
         <v>0</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>286</v>
+        <v>330</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="J12" s="6" t="s">
-        <v>151</v>
+        <v>195</v>
       </c>
       <c r="K12" s="6" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="L12" s="6" t="s">
-        <v>152</v>
+        <v>196</v>
       </c>
       <c r="AA12" s="6" t="s">
-        <v>287</v>
+        <v>331</v>
       </c>
       <c r="AT12" s="6" t="s">
-        <v>163</v>
+        <v>207</v>
       </c>
       <c r="AU12" s="6">
         <v>1</v>
@@ -4692,319 +4991,319 @@
     </row>
     <row r="13">
       <c r="B13" s="5" t="s">
-        <v>251</v>
+        <v>295</v>
       </c>
       <c r="C13" s="5">
         <v>0</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>297</v>
+        <v>341</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="J13" s="5" t="s">
-        <v>151</v>
+        <v>195</v>
       </c>
       <c r="K13" s="5" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="L13" s="5" t="s">
-        <v>152</v>
+        <v>196</v>
       </c>
       <c r="AA13" s="5" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="6" t="s">
-        <v>253</v>
+        <v>297</v>
       </c>
       <c r="C14" s="6">
         <v>0</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>297</v>
+        <v>341</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="J14" s="6" t="s">
-        <v>151</v>
+        <v>195</v>
       </c>
       <c r="K14" s="6" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="L14" s="6" t="s">
-        <v>152</v>
+        <v>196</v>
       </c>
       <c r="AA14" s="6" t="s">
-        <v>299</v>
+        <v>343</v>
       </c>
       <c r="AT14" s="6" t="s">
-        <v>300</v>
+        <v>344</v>
       </c>
       <c r="AU14" s="6">
         <v>1</v>
       </c>
       <c r="BK14" s="6" t="s">
-        <v>301</v>
+        <v>345</v>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="5" t="s">
-        <v>255</v>
+        <v>299</v>
       </c>
       <c r="C15" s="5">
         <v>0</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>297</v>
+        <v>341</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="I15" s="5" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="J15" s="5" t="s">
-        <v>151</v>
+        <v>195</v>
       </c>
       <c r="K15" s="5" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="L15" s="5" t="s">
-        <v>152</v>
+        <v>196</v>
       </c>
       <c r="AA15" s="5" t="s">
-        <v>299</v>
+        <v>343</v>
       </c>
       <c r="AT15" s="5" t="s">
-        <v>300</v>
+        <v>344</v>
       </c>
       <c r="AU15" s="5">
         <v>1</v>
       </c>
       <c r="BK15" s="5" t="s">
-        <v>302</v>
+        <v>346</v>
       </c>
     </row>
     <row r="16">
       <c r="B16" s="6" t="s">
-        <v>257</v>
+        <v>301</v>
       </c>
       <c r="C16" s="6">
         <v>0</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>297</v>
+        <v>341</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="J16" s="6" t="s">
-        <v>151</v>
+        <v>195</v>
       </c>
       <c r="K16" s="6" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="L16" s="6" t="s">
-        <v>152</v>
+        <v>196</v>
       </c>
       <c r="AA16" s="6" t="s">
-        <v>299</v>
+        <v>343</v>
       </c>
       <c r="AT16" s="6" t="s">
-        <v>300</v>
+        <v>344</v>
       </c>
       <c r="AU16" s="6">
         <v>1</v>
       </c>
       <c r="BK16" s="6" t="s">
-        <v>303</v>
+        <v>347</v>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="5" t="s">
-        <v>259</v>
+        <v>303</v>
       </c>
       <c r="C17" s="5">
         <v>0</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>297</v>
+        <v>341</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="I17" s="5" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="J17" s="5" t="s">
-        <v>151</v>
+        <v>195</v>
       </c>
       <c r="K17" s="5" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="L17" s="5" t="s">
-        <v>152</v>
+        <v>196</v>
       </c>
       <c r="AA17" s="5" t="s">
-        <v>299</v>
+        <v>343</v>
       </c>
       <c r="AT17" s="5" t="s">
-        <v>300</v>
+        <v>344</v>
       </c>
       <c r="AU17" s="5">
         <v>1</v>
       </c>
       <c r="BK17" s="5" t="s">
-        <v>304</v>
+        <v>348</v>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="6" t="s">
-        <v>261</v>
+        <v>305</v>
       </c>
       <c r="C18" s="6">
         <v>0</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>297</v>
+        <v>341</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="I18" s="6" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="J18" s="6" t="s">
-        <v>151</v>
+        <v>195</v>
       </c>
       <c r="K18" s="6" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="L18" s="6" t="s">
-        <v>152</v>
+        <v>196</v>
       </c>
       <c r="AA18" s="6" t="s">
-        <v>299</v>
+        <v>343</v>
       </c>
       <c r="AT18" s="6" t="s">
-        <v>300</v>
+        <v>344</v>
       </c>
       <c r="AU18" s="6">
         <v>1</v>
       </c>
       <c r="BK18" s="6" t="s">
-        <v>305</v>
+        <v>349</v>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="5" t="s">
-        <v>263</v>
+        <v>307</v>
       </c>
       <c r="C19" s="5">
         <v>0</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>297</v>
+        <v>341</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="H19" s="5" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="I19" s="5" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="J19" s="5" t="s">
-        <v>151</v>
+        <v>195</v>
       </c>
       <c r="K19" s="5" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="L19" s="5" t="s">
-        <v>152</v>
+        <v>196</v>
       </c>
       <c r="AA19" s="5" t="s">
-        <v>306</v>
+        <v>350</v>
       </c>
       <c r="AF19" s="5" t="s">
-        <v>307</v>
+        <v>351</v>
       </c>
       <c r="AG19" s="5" t="s">
-        <v>308</v>
+        <v>352</v>
       </c>
       <c r="AH19" s="5">
         <v>1</v>
@@ -5012,46 +5311,46 @@
     </row>
     <row r="20">
       <c r="B20" s="6" t="s">
-        <v>265</v>
+        <v>309</v>
       </c>
       <c r="C20" s="6">
         <v>0</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>297</v>
+        <v>341</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="I20" s="6" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="J20" s="6" t="s">
-        <v>151</v>
+        <v>195</v>
       </c>
       <c r="K20" s="6" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="L20" s="6" t="s">
-        <v>152</v>
+        <v>196</v>
       </c>
       <c r="AA20" s="6" t="s">
-        <v>306</v>
+        <v>350</v>
       </c>
       <c r="AF20" s="6" t="s">
-        <v>309</v>
+        <v>353</v>
       </c>
       <c r="AG20" s="6" t="s">
-        <v>308</v>
+        <v>352</v>
       </c>
       <c r="AH20" s="6">
         <v>1</v>
@@ -5059,219 +5358,219 @@
     </row>
     <row r="21">
       <c r="B21" s="5" t="s">
-        <v>267</v>
+        <v>311</v>
       </c>
       <c r="C21" s="5">
         <v>0</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>286</v>
+        <v>330</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="H21" s="5" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="I21" s="5" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="J21" s="5" t="s">
-        <v>151</v>
+        <v>195</v>
       </c>
       <c r="K21" s="5" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="L21" s="5" t="s">
-        <v>152</v>
+        <v>196</v>
       </c>
       <c r="AA21" s="5" t="s">
-        <v>153</v>
+        <v>197</v>
       </c>
       <c r="AH21" s="5">
         <v>1</v>
       </c>
       <c r="BF21" s="5" t="s">
-        <v>310</v>
+        <v>354</v>
       </c>
       <c r="BH21" s="5" t="s">
-        <v>311</v>
+        <v>355</v>
       </c>
     </row>
     <row r="22">
       <c r="B22" s="6" t="s">
-        <v>269</v>
+        <v>313</v>
       </c>
       <c r="C22" s="6">
         <v>0</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>286</v>
+        <v>330</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="I22" s="6" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="J22" s="6" t="s">
-        <v>151</v>
+        <v>195</v>
       </c>
       <c r="K22" s="6" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="L22" s="6" t="s">
-        <v>152</v>
+        <v>196</v>
       </c>
       <c r="AA22" s="6" t="s">
-        <v>153</v>
+        <v>197</v>
       </c>
       <c r="AH22" s="6">
         <v>1</v>
       </c>
       <c r="BF22" s="6" t="s">
-        <v>312</v>
+        <v>356</v>
       </c>
       <c r="BH22" s="6" t="s">
-        <v>311</v>
+        <v>355</v>
       </c>
     </row>
     <row r="23">
       <c r="B23" s="5" t="s">
-        <v>271</v>
+        <v>315</v>
       </c>
       <c r="C23" s="5">
         <v>0</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>297</v>
+        <v>341</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="H23" s="5" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="I23" s="5" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="J23" s="5" t="s">
-        <v>151</v>
+        <v>195</v>
       </c>
       <c r="K23" s="5" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="L23" s="5" t="s">
-        <v>152</v>
+        <v>196</v>
       </c>
       <c r="AA23" s="5" t="s">
-        <v>313</v>
+        <v>357</v>
       </c>
     </row>
     <row r="24">
       <c r="B24" s="6" t="s">
-        <v>273</v>
+        <v>317</v>
       </c>
       <c r="C24" s="6">
         <v>0</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>297</v>
+        <v>341</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="I24" s="6" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="J24" s="6" t="s">
-        <v>151</v>
+        <v>195</v>
       </c>
       <c r="K24" s="6" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="L24" s="6" t="s">
-        <v>152</v>
+        <v>196</v>
       </c>
       <c r="AA24" s="6" t="s">
-        <v>153</v>
+        <v>197</v>
       </c>
       <c r="AH24" s="6">
         <v>3</v>
       </c>
       <c r="BF24" s="6" t="s">
-        <v>178</v>
+        <v>222</v>
       </c>
       <c r="BH24" s="6" t="s">
-        <v>314</v>
+        <v>358</v>
       </c>
     </row>
     <row r="25">
       <c r="B25" s="5" t="s">
-        <v>275</v>
+        <v>319</v>
       </c>
       <c r="C25" s="5">
         <v>0</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>297</v>
+        <v>341</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="H25" s="5" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="I25" s="5" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="J25" s="5" t="s">
-        <v>151</v>
+        <v>195</v>
       </c>
       <c r="K25" s="5" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="L25" s="5" t="s">
-        <v>152</v>
+        <v>196</v>
       </c>
       <c r="AA25" s="5" t="s">
-        <v>315</v>
+        <v>359</v>
       </c>
       <c r="AE25" s="5">
         <v>40</v>
@@ -5282,46 +5581,46 @@
     </row>
     <row r="26">
       <c r="B26" s="6" t="s">
-        <v>277</v>
+        <v>321</v>
       </c>
       <c r="C26" s="6">
         <v>0</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>297</v>
+        <v>341</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="F26" s="6" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="I26" s="6" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="J26" s="6" t="s">
-        <v>151</v>
+        <v>195</v>
       </c>
       <c r="K26" s="6" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="L26" s="6" t="s">
-        <v>152</v>
+        <v>196</v>
       </c>
       <c r="AA26" s="6" t="s">
-        <v>306</v>
+        <v>350</v>
       </c>
       <c r="AF26" s="6" t="s">
-        <v>316</v>
+        <v>360</v>
       </c>
       <c r="AG26" s="6" t="s">
-        <v>308</v>
+        <v>352</v>
       </c>
       <c r="AH26" s="6">
         <v>5</v>
@@ -5329,43 +5628,43 @@
     </row>
     <row r="27">
       <c r="B27" s="5" t="s">
-        <v>279</v>
+        <v>323</v>
       </c>
       <c r="C27" s="5">
         <v>0</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>297</v>
+        <v>341</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="H27" s="5" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="I27" s="5" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="J27" s="5" t="s">
-        <v>151</v>
+        <v>195</v>
       </c>
       <c r="K27" s="5" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="L27" s="5" t="s">
-        <v>152</v>
+        <v>196</v>
       </c>
       <c r="AA27" s="5" t="s">
-        <v>317</v>
+        <v>361</v>
       </c>
       <c r="AR27" s="5" t="s">
-        <v>318</v>
+        <v>362</v>
       </c>
       <c r="AS27" s="5">
         <v>3</v>
@@ -5373,49 +5672,49 @@
     </row>
     <row r="28">
       <c r="B28" s="6" t="s">
-        <v>281</v>
+        <v>325</v>
       </c>
       <c r="C28" s="6">
         <v>0</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>297</v>
+        <v>341</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="F28" s="6" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="I28" s="6" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="J28" s="6" t="s">
-        <v>151</v>
+        <v>195</v>
       </c>
       <c r="K28" s="6" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="L28" s="6" t="s">
-        <v>152</v>
+        <v>196</v>
       </c>
       <c r="AA28" s="6" t="s">
-        <v>299</v>
+        <v>343</v>
       </c>
       <c r="AT28" s="6" t="s">
-        <v>288</v>
+        <v>332</v>
       </c>
       <c r="AU28" s="6">
         <v>2</v>
       </c>
       <c r="AX28" s="6" t="s">
-        <v>319</v>
+        <v>363</v>
       </c>
     </row>
   </sheetData>

--- a/samples/clover/design-data/xlsx/Setup.xlsx
+++ b/samples/clover/design-data/xlsx/Setup.xlsx
@@ -11,19 +11,27 @@
     <sheet name="Stake" sheetId="3" r:id="rId5"/>
     <sheet name="Tag" sheetId="4" r:id="rId6"/>
     <sheet name="TagEffect" sheetId="5" r:id="rId7"/>
+    <sheet name="Challenge" sheetId="6" r:id="rId8"/>
+    <sheet name="ChallengeEffect" sheetId="7" r:id="rId9"/>
+    <sheet name="ChallengeBan" sheetId="8" r:id="rId10"/>
+    <sheet name="ChallengeCard" sheetId="9" r:id="rId11"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1"><![CDATA[Deck!$B$2:$H$19]]></definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1"><![CDATA[DeckEffect!$B$2:$BL$29]]></definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1"><![CDATA[DeckEffect!$B$2:$BM$29]]></definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1"><![CDATA[Stake!$B$2:$H$12]]></definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1"><![CDATA[Tag!$B$2:$E$28]]></definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1"><![CDATA[TagEffect!$B$2:$BL$28]]></definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1"><![CDATA[TagEffect!$B$2:$BM$28]]></definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1"><![CDATA[Challenge!$B$2:$E$24]]></definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1"><![CDATA[ChallengeEffect!$B$2:$BM$63]]></definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1"><![CDATA[ChallengeBan!$B$2:$E$78]]></definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1"><![CDATA[ChallengeCard!$B$2:$I$11]]></definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1031" uniqueCount="364">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2277" uniqueCount="549">
   <si>
     <t xml:space="preserve">:table Deck(key=deck_id)</t>
   </si>
@@ -538,6 +546,9 @@
     <t xml:space="preserve">operation.handler</t>
   </si>
   <si>
+    <t xml:space="preserve">operation.sticker</t>
+  </si>
+  <si>
     <t xml:space="preserve">foreign Deck</t>
   </si>
   <si>
@@ -1115,6 +1126,558 @@
   </si>
   <si>
     <t xml:space="preserve">Common</t>
+  </si>
+  <si>
+    <t xml:space="preserve">:table Challenge(key=challenge_id)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">런의 시작 조건을 통째로 바꾼 판입니다. 덱·스테이크와 나란한 세 번째 축이고, 앞의 것을 깨야 다음이 열립니다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">challenge_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string (text=Challenge)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">int (min=1, max=20)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">해금 순서</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dry_season</t>
+  </si>
+  <si>
+    <t xml:space="preserve">마른 철</t>
+  </si>
+  <si>
+    <t xml:space="preserve">덱 5종으로 승리</t>
+  </si>
+  <si>
+    <t xml:space="preserve">face_town</t>
+  </si>
+  <si>
+    <t xml:space="preserve">그림 마을</t>
+  </si>
+  <si>
+    <t xml:space="preserve">coin_ceiling</t>
+  </si>
+  <si>
+    <t xml:space="preserve">동전 천장</t>
+  </si>
+  <si>
+    <t xml:space="preserve">shear_edge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">가위날</t>
+  </si>
+  <si>
+    <t xml:space="preserve">blind_draw</t>
+  </si>
+  <si>
+    <t xml:space="preserve">엎어진 패</t>
+  </si>
+  <si>
+    <t xml:space="preserve">low_field</t>
+  </si>
+  <si>
+    <t xml:space="preserve">낮은 들</t>
+  </si>
+  <si>
+    <t xml:space="preserve">엎어진 패 격파</t>
+  </si>
+  <si>
+    <t xml:space="preserve">heavy_purse</t>
+  </si>
+  <si>
+    <t xml:space="preserve">무거운 지갑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">낮은 들 격파</t>
+  </si>
+  <si>
+    <t xml:space="preserve">evergreen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">상록</t>
+  </si>
+  <si>
+    <t xml:space="preserve">무거운 지갑 격파</t>
+  </si>
+  <si>
+    <t xml:space="preserve">stone_court</t>
+  </si>
+  <si>
+    <t xml:space="preserve">돌이 된 얼굴</t>
+  </si>
+  <si>
+    <t xml:space="preserve">상록 격파</t>
+  </si>
+  <si>
+    <t xml:space="preserve">red_wax</t>
+  </si>
+  <si>
+    <t xml:space="preserve">붉은 밀랍</t>
+  </si>
+  <si>
+    <t xml:space="preserve">돌이 된 얼굴 격파</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sealed_fate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">굳는 편성</t>
+  </si>
+  <si>
+    <t xml:space="preserve">붉은 밀랍 격파</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rising_price</t>
+  </si>
+  <si>
+    <t xml:space="preserve">오르는 값</t>
+  </si>
+  <si>
+    <t xml:space="preserve">굳는 편성 격파</t>
+  </si>
+  <si>
+    <t xml:space="preserve">vine_night</t>
+  </si>
+  <si>
+    <t xml:space="preserve">덩굴의 밤</t>
+  </si>
+  <si>
+    <t xml:space="preserve">오르는 값 격파</t>
+  </si>
+  <si>
+    <t xml:space="preserve">glass_field</t>
+  </si>
+  <si>
+    <t xml:space="preserve">유리밭</t>
+  </si>
+  <si>
+    <t xml:space="preserve">덩굴의 밤 격파</t>
+  </si>
+  <si>
+    <t xml:space="preserve">stone_row</t>
+  </si>
+  <si>
+    <t xml:space="preserve">돌의 줄</t>
+  </si>
+  <si>
+    <t xml:space="preserve">유리밭 격파</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sky_road</t>
+  </si>
+  <si>
+    <t xml:space="preserve">하늘길</t>
+  </si>
+  <si>
+    <t xml:space="preserve">돌의 줄 격파</t>
+  </si>
+  <si>
+    <t xml:space="preserve">five_leaves</t>
+  </si>
+  <si>
+    <t xml:space="preserve">다섯 잎</t>
+  </si>
+  <si>
+    <t xml:space="preserve">하늘길 격파</t>
+  </si>
+  <si>
+    <t xml:space="preserve">single_thread</t>
+  </si>
+  <si>
+    <t xml:space="preserve">한 올</t>
+  </si>
+  <si>
+    <t xml:space="preserve">다섯 잎 격파</t>
+  </si>
+  <si>
+    <t xml:space="preserve">barren_road</t>
+  </si>
+  <si>
+    <t xml:space="preserve">메마른 길</t>
+  </si>
+  <si>
+    <t xml:space="preserve">한 올 격파</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bare_field</t>
+  </si>
+  <si>
+    <t xml:space="preserve">맨 밭</t>
+  </si>
+  <si>
+    <t xml:space="preserve">메마른 길 격파</t>
+  </si>
+  <si>
+    <t xml:space="preserve">:table ChallengeEffect(key="owner,order")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">챌린지가 정하는 시작 조건입니다. `DeckEffect` 와 컬럼 구성이 같고 소유자만 다릅니다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">foreign Challenge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NoSmallBlindReward</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NoBigBlindReward</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NoBossBlindReward</t>
+  </si>
+  <si>
+    <t xml:space="preserve">seed_pod</t>
+  </si>
+  <si>
+    <t xml:space="preserve">long_path</t>
+  </si>
+  <si>
+    <t xml:space="preserve">stepping_stone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ChipsCappedByMoney</t>
+  </si>
+  <si>
+    <t xml:space="preserve">seed_money</t>
+  </si>
+  <si>
+    <t xml:space="preserve">money_tree</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PinnedJokerSlot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pruning_shears</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FaceDownDrawRate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">face_pattern</t>
+  </si>
+  <si>
+    <t xml:space="preserve">trade_card</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HandSizePerMoney</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AllJokersEternal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pebble_jar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DebuffPlayedAfterScoring</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CondAnteAtLeast</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PriceRisePerPurchase</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ledger_note</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NoJokersInShop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">leech_vine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">the_emperor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">the_empress</t>
+  </si>
+  <si>
+    <t xml:space="preserve">magic_trick</t>
+  </si>
+  <si>
+    <t xml:space="preserve">illusion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">loaded_dice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">standing_stone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">star_chart</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sky_rocket</t>
+  </si>
+  <si>
+    <t xml:space="preserve">planet_tycoon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sharper</t>
+  </si>
+  <si>
+    <t xml:space="preserve">twig</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DiscardCost</t>
+  </si>
+  <si>
+    <t xml:space="preserve">:table ChallengeBan(key="owner,order")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">챌린지가 금지하는 것입니다. 금지된 것은 어느 경로로도 나오지 않습니다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kind</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ref_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">int (min=0, max=63)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BanKind</t>
+  </si>
+  <si>
+    <t xml:space="preserve">어느 챌린지</t>
+  </si>
+  <si>
+    <t xml:space="preserve">무엇의 갈래</t>
+  </si>
+  <si>
+    <t xml:space="preserve">금지되는 것의 식별자</t>
+  </si>
+  <si>
+    <t xml:space="preserve">moon_ladder</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gilt_coin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">orbit_dish</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Boss</t>
+  </si>
+  <si>
+    <t xml:space="preserve">the_plant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">windfall_pear</t>
+  </si>
+  <si>
+    <t xml:space="preserve">orchard_pear</t>
+  </si>
+  <si>
+    <t xml:space="preserve">frost_pane</t>
+  </si>
+  <si>
+    <t xml:space="preserve">broad_bean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">noodle_pot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">soda_cap</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fizz_bottle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">puffball</t>
+  </si>
+  <si>
+    <t xml:space="preserve">old_bones</t>
+  </si>
+  <si>
+    <t xml:space="preserve">faint_outline</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ring_fighter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">verdant_leaf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">clearance_sale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">liquidation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gilt_mask</t>
+  </si>
+  <si>
+    <t xml:space="preserve">deed_stamp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">the_magician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">the_hierophant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">the_chariot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">the_devil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">the_tower</t>
+  </si>
+  <si>
+    <t xml:space="preserve">the_lovers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">incantation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">grim</t>
+  </si>
+  <si>
+    <t xml:space="preserve">familiar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">standard_normal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">standard_jumbo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tag</t>
+  </si>
+  <si>
+    <t xml:space="preserve">night_thief</t>
+  </si>
+  <si>
+    <t xml:space="preserve">grabber</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nacho_tong</t>
+  </si>
+  <si>
+    <t xml:space="preserve">spinner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fiddler</t>
+  </si>
+  <si>
+    <t xml:space="preserve">judgement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">the_wheel_of_fortune</t>
+  </si>
+  <si>
+    <t xml:space="preserve">temperance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wraith</t>
+  </si>
+  <si>
+    <t xml:space="preserve">the_soul</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ectoplasm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ankh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">crimson_heart</t>
+  </si>
+  <si>
+    <t xml:space="preserve">amber_acorn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">antimatter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">buffoon_normal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">buffoon_jumbo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">:table ChallengeCard(key="owner,order")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">챌린지의 시작 덱입니다. **행이 없으면 표준 52장입니다** — 20종 중 15종이 그렇습니다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">copies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">enhancement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">seal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">edition</t>
+  </si>
+  <si>
+    <t xml:space="preserve">int (min=0, max=4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EnhancementKind</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SealKind</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EditionKind</t>
+  </si>
+  <si>
+    <t xml:space="preserve">순서</t>
+  </si>
+  <si>
+    <t xml:space="preserve">어느 랭크들</t>
+  </si>
+  <si>
+    <t xml:space="preserve">어느 무늬들. 비우면 넷 다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">몇 벌</t>
+  </si>
+  <si>
+    <t xml:space="preserve">강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">인장</t>
+  </si>
+  <si>
+    <t xml:space="preserve">에디션</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Four;Five;Six;Seven;Eight;Nine;Ten</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Base</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jack;Queen;King</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Two;Three;Four;Five;Six;Seven;Eight;Nine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Two;Three;Four;Five;Six;Seven;Eight;Nine;Ten;Ace</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Two;Three;Four;Five;Six;Seven;Eight;Nine;Ten;Jack;Queen;King;Ace</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Glass</t>
   </si>
 </sst>
 </file>
@@ -1771,7 +2334,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:BL29"/>
+  <dimension ref="A1:BM29"/>
   <sheetFormatPr defaultColWidth="8.43" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="44.53125" customWidth="1"/>
@@ -1822,7 +2385,7 @@
     <col min="59" max="60" width="23.4375" customWidth="1"/>
     <col min="61" max="61" width="18.75" customWidth="1"/>
     <col min="62" max="63" width="21.09375" customWidth="1"/>
-    <col min="64" max="64" width="22.265625" customWidth="1"/>
+    <col min="64" max="65" width="22.265625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1894,6 +2457,7 @@
       <c r="BJ1" s="2"/>
       <c r="BK1" s="2"/>
       <c r="BL1" s="2"/>
+      <c r="BM1" s="2"/>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
@@ -2088,43 +2652,46 @@
       <c r="BL2" s="4" t="s">
         <v>170</v>
       </c>
+      <c r="BM2" s="4" t="s">
+        <v>171</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
         <v>10</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="G3" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="K3" s="4" t="s">
         <v>175</v>
       </c>
-      <c r="H3" s="4" t="s">
-        <v>176</v>
-      </c>
-      <c r="I3" s="4" t="s">
-        <v>177</v>
-      </c>
-      <c r="J3" s="4" t="s">
-        <v>178</v>
-      </c>
-      <c r="K3" s="4" t="s">
-        <v>174</v>
-      </c>
       <c r="L3" s="4" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="M3" s="4"/>
       <c r="N3" s="4"/>
@@ -2141,7 +2708,7 @@
       <c r="Y3" s="4"/>
       <c r="Z3" s="4"/>
       <c r="AA3" s="4" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="AB3" s="4"/>
       <c r="AC3" s="4"/>
@@ -2180,43 +2747,44 @@
       <c r="BJ3" s="4"/>
       <c r="BK3" s="4"/>
       <c r="BL3" s="4"/>
+      <c r="BM3" s="4"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
         <v>17</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="L4" s="4" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="M4" s="4"/>
       <c r="N4" s="4"/>
@@ -2233,7 +2801,7 @@
       <c r="Y4" s="4"/>
       <c r="Z4" s="4"/>
       <c r="AA4" s="4" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AB4" s="4"/>
       <c r="AC4" s="4"/>
@@ -2272,6 +2840,7 @@
       <c r="BJ4" s="4"/>
       <c r="BK4" s="4"/>
       <c r="BL4" s="4"/>
+      <c r="BM4" s="4"/>
     </row>
     <row r="5">
       <c r="B5" s="5" t="s">
@@ -2281,40 +2850,40 @@
         <v>0</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="J5" s="5" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="K5" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="L5" s="5" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AA5" s="5" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AH5" s="5">
         <v>1</v>
       </c>
       <c r="BF5" s="5" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="6">
@@ -2325,40 +2894,40 @@
         <v>0</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="J6" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="K6" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="L6" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AA6" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AH6" s="6">
         <v>1</v>
       </c>
       <c r="BF6" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="7">
@@ -2369,40 +2938,40 @@
         <v>0</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="K7" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="L7" s="5" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AA7" s="5" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AH7" s="5">
         <v>10</v>
       </c>
       <c r="BF7" s="5" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="8">
@@ -2413,40 +2982,40 @@
         <v>0</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="J8" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="K8" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="L8" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AA8" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AH8" s="6">
         <v>1</v>
       </c>
       <c r="BF8" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="9">
@@ -2457,40 +3026,40 @@
         <v>1</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="K9" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="L9" s="5" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AA9" s="5" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AH9" s="5">
         <v>2</v>
       </c>
       <c r="BF9" s="5" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="10">
@@ -2501,40 +3070,40 @@
         <v>2</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="J10" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="K10" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="L10" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AA10" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AH10" s="6">
         <v>1</v>
       </c>
       <c r="BF10" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="11">
@@ -2545,40 +3114,40 @@
         <v>0</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="J11" s="5" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="K11" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="L11" s="5" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AA11" s="5" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AH11" s="5">
         <v>1</v>
       </c>
       <c r="BF11" s="5" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="12">
@@ -2589,40 +3158,40 @@
         <v>1</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="J12" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="K12" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="L12" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AA12" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AH12" s="6">
         <v>-1</v>
       </c>
       <c r="BF12" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="13">
@@ -2633,43 +3202,43 @@
         <v>0</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="J13" s="5" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="K13" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="L13" s="5" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AA13" s="5" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="AT13" s="5" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AU13" s="5">
         <v>1</v>
       </c>
       <c r="BK13" s="5" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="14">
@@ -2680,43 +3249,43 @@
         <v>1</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="J14" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="K14" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="L14" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AA14" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="AT14" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AU14" s="6">
         <v>2</v>
       </c>
       <c r="BK14" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="15">
@@ -2727,43 +3296,43 @@
         <v>0</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I15" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="J15" s="5" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="K15" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="L15" s="5" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AA15" s="5" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="AT15" s="5" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AU15" s="5">
         <v>1</v>
       </c>
       <c r="BK15" s="5" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="16">
@@ -2774,40 +3343,40 @@
         <v>1</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="J16" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="K16" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="L16" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AA16" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AH16" s="6">
         <v>-1</v>
       </c>
       <c r="BF16" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="17">
@@ -2818,40 +3387,40 @@
         <v>0</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I17" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="J17" s="5" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="K17" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="L17" s="5" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AA17" s="5" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AH17" s="5">
         <v>1</v>
       </c>
       <c r="BF17" s="5" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="18">
@@ -2862,43 +3431,43 @@
         <v>1</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I18" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="J18" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="K18" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="L18" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AA18" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="AT18" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AU18" s="6">
         <v>1</v>
       </c>
       <c r="BK18" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="19">
@@ -2909,40 +3478,40 @@
         <v>0</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H19" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I19" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="J19" s="5" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="K19" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="L19" s="5" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AA19" s="5" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AH19" s="5">
         <v>1</v>
       </c>
       <c r="BF19" s="5" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="20">
@@ -2953,40 +3522,40 @@
         <v>0</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I20" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="J20" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="K20" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="L20" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AA20" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AH20" s="6">
         <v>1</v>
       </c>
       <c r="BF20" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="21">
@@ -2997,43 +3566,43 @@
         <v>0</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H21" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I21" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="J21" s="5" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="K21" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="L21" s="5" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AA21" s="5" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="AT21" s="5" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AU21" s="5">
         <v>1</v>
       </c>
       <c r="BK21" s="5" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="22">
@@ -3044,43 +3613,43 @@
         <v>1</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I22" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="J22" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="K22" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="L22" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AA22" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="AT22" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AU22" s="6">
         <v>1</v>
       </c>
       <c r="BK22" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="23">
@@ -3091,43 +3660,43 @@
         <v>2</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H23" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I23" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="J23" s="5" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="K23" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="L23" s="5" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AA23" s="5" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="AT23" s="5" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AU23" s="5">
         <v>1</v>
       </c>
       <c r="BK23" s="5" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="24">
@@ -3138,40 +3707,40 @@
         <v>0</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I24" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="J24" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="K24" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="L24" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AA24" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AH24" s="6">
         <v>2</v>
       </c>
       <c r="BF24" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="25">
@@ -3182,40 +3751,40 @@
         <v>1</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H25" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I25" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="J25" s="5" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="K25" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="L25" s="5" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AA25" s="5" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AH25" s="5">
         <v>-1</v>
       </c>
       <c r="BF25" s="5" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="26">
@@ -3226,40 +3795,40 @@
         <v>0</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F26" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I26" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="J26" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="K26" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="L26" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AA26" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AH26" s="6">
         <v>1</v>
       </c>
       <c r="BF26" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="27">
@@ -3270,40 +3839,40 @@
         <v>0</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H27" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I27" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="J27" s="5" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="K27" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="L27" s="5" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AA27" s="5" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AH27" s="5">
         <v>1</v>
       </c>
       <c r="BF27" s="5" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="28">
@@ -3314,43 +3883,43 @@
         <v>1</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F28" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I28" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="J28" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="K28" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="L28" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AA28" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AH28" s="6">
         <v>20000</v>
       </c>
       <c r="BF28" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="BG28" s="6" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="29">
@@ -3361,44 +3930,44 @@
         <v>0</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H29" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I29" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="J29" s="5" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="K29" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="L29" s="5" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AA29" s="5" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AH29" s="5">
         <v>1</v>
       </c>
       <c r="BF29" s="5" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B2:BL29"/>
+  <autoFilter ref="B2:BM29"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -3419,10 +3988,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
@@ -3436,25 +4005,25 @@
         <v>2</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>4</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="3">
@@ -3462,25 +4031,25 @@
         <v>10</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="4">
@@ -3488,33 +4057,33 @@
         <v>17</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>19</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="5">
       <c r="B5" s="5" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D5" s="5">
         <v>1</v>
@@ -3526,7 +4095,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H5" s="5">
         <v>0</v>
@@ -3534,10 +4103,10 @@
     </row>
     <row r="6">
       <c r="B6" s="6" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D6" s="6">
         <v>1</v>
@@ -3549,7 +4118,7 @@
         <v>0</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H6" s="6">
         <v>0</v>
@@ -3557,10 +4126,10 @@
     </row>
     <row r="7">
       <c r="B7" s="5" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D7" s="5">
         <v>2</v>
@@ -3572,7 +4141,7 @@
         <v>0</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H7" s="5">
         <v>0</v>
@@ -3580,10 +4149,10 @@
     </row>
     <row r="8">
       <c r="B8" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D8" s="6">
         <v>2</v>
@@ -3595,7 +4164,7 @@
         <v>0</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H8" s="6">
         <v>30</v>
@@ -3603,10 +4172,10 @@
     </row>
     <row r="9">
       <c r="B9" s="5" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D9" s="5">
         <v>2</v>
@@ -3618,7 +4187,7 @@
         <v>-1</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H9" s="5">
         <v>30</v>
@@ -3626,10 +4195,10 @@
     </row>
     <row r="10">
       <c r="B10" s="6" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D10" s="6">
         <v>3</v>
@@ -3641,7 +4210,7 @@
         <v>-1</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H10" s="6">
         <v>30</v>
@@ -3649,10 +4218,10 @@
     </row>
     <row r="11">
       <c r="B11" s="5" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D11" s="5">
         <v>3</v>
@@ -3664,7 +4233,7 @@
         <v>-1</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H11" s="5">
         <v>30</v>
@@ -3672,10 +4241,10 @@
     </row>
     <row r="12">
       <c r="B12" s="6" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D12" s="6">
         <v>3</v>
@@ -3687,7 +4256,7 @@
         <v>-1</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H12" s="6">
         <v>30</v>
@@ -3713,10 +4282,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
@@ -3727,13 +4296,13 @@
         <v>2</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>4</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="E2" s="4" t="s">
         <v>6</v>
@@ -3744,16 +4313,16 @@
         <v>10</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="4">
@@ -3767,18 +4336,18 @@
         <v>19</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="5">
       <c r="B5" s="5" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D5" s="5">
         <v>1</v>
@@ -3789,10 +4358,10 @@
     </row>
     <row r="6">
       <c r="B6" s="6" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="D6" s="6">
         <v>1</v>
@@ -3803,10 +4372,10 @@
     </row>
     <row r="7">
       <c r="B7" s="5" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="D7" s="5">
         <v>2</v>
@@ -3817,10 +4386,10 @@
     </row>
     <row r="8">
       <c r="B8" s="6" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D8" s="6">
         <v>1</v>
@@ -3831,10 +4400,10 @@
     </row>
     <row r="9">
       <c r="B9" s="5" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D9" s="5">
         <v>1</v>
@@ -3845,10 +4414,10 @@
     </row>
     <row r="10">
       <c r="B10" s="6" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D10" s="6">
         <v>1</v>
@@ -3859,10 +4428,10 @@
     </row>
     <row r="11">
       <c r="B11" s="5" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D11" s="5">
         <v>1</v>
@@ -3873,10 +4442,10 @@
     </row>
     <row r="12">
       <c r="B12" s="6" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D12" s="6">
         <v>1</v>
@@ -3887,10 +4456,10 @@
     </row>
     <row r="13">
       <c r="B13" s="5" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D13" s="5">
         <v>1</v>
@@ -3901,10 +4470,10 @@
     </row>
     <row r="14">
       <c r="B14" s="6" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="D14" s="6">
         <v>2</v>
@@ -3915,10 +4484,10 @@
     </row>
     <row r="15">
       <c r="B15" s="5" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="D15" s="5">
         <v>1</v>
@@ -3929,10 +4498,10 @@
     </row>
     <row r="16">
       <c r="B16" s="6" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D16" s="6">
         <v>2</v>
@@ -3943,10 +4512,10 @@
     </row>
     <row r="17">
       <c r="B17" s="5" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D17" s="5">
         <v>2</v>
@@ -3957,10 +4526,10 @@
     </row>
     <row r="18">
       <c r="B18" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="D18" s="6">
         <v>2</v>
@@ -3971,10 +4540,10 @@
     </row>
     <row r="19">
       <c r="B19" s="5" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D19" s="5">
         <v>2</v>
@@ -3985,10 +4554,10 @@
     </row>
     <row r="20">
       <c r="B20" s="6" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="D20" s="6">
         <v>2</v>
@@ -3999,10 +4568,10 @@
     </row>
     <row r="21">
       <c r="B21" s="5" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="D21" s="5">
         <v>1</v>
@@ -4013,10 +4582,10 @@
     </row>
     <row r="22">
       <c r="B22" s="6" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="D22" s="6">
         <v>1</v>
@@ -4027,10 +4596,10 @@
     </row>
     <row r="23">
       <c r="B23" s="5" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="D23" s="5">
         <v>1</v>
@@ -4041,10 +4610,10 @@
     </row>
     <row r="24">
       <c r="B24" s="6" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="D24" s="6">
         <v>1</v>
@@ -4055,10 +4624,10 @@
     </row>
     <row r="25">
       <c r="B25" s="5" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="D25" s="5">
         <v>1</v>
@@ -4069,10 +4638,10 @@
     </row>
     <row r="26">
       <c r="B26" s="6" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D26" s="6">
         <v>1</v>
@@ -4083,10 +4652,10 @@
     </row>
     <row r="27">
       <c r="B27" s="5" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="D27" s="5">
         <v>2</v>
@@ -4097,10 +4666,10 @@
     </row>
     <row r="28">
       <c r="B28" s="6" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="D28" s="6">
         <v>2</v>
@@ -4117,7 +4686,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:BL28"/>
+  <dimension ref="A1:BM28"/>
   <sheetFormatPr defaultColWidth="8.43" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="43.359375" customWidth="1"/>
@@ -4171,15 +4740,15 @@
     <col min="59" max="60" width="23.4375" customWidth="1"/>
     <col min="61" max="61" width="18.75" customWidth="1"/>
     <col min="62" max="63" width="21.09375" customWidth="1"/>
-    <col min="64" max="64" width="22.265625" customWidth="1"/>
+    <col min="64" max="65" width="22.265625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
@@ -4243,6 +4812,7 @@
       <c r="BJ1" s="2"/>
       <c r="BK1" s="2"/>
       <c r="BL1" s="2"/>
+      <c r="BM1" s="2"/>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
@@ -4437,43 +5007,46 @@
       <c r="BL2" s="4" t="s">
         <v>170</v>
       </c>
+      <c r="BM2" s="4" t="s">
+        <v>171</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
         <v>10</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="G3" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="K3" s="4" t="s">
         <v>175</v>
       </c>
-      <c r="H3" s="4" t="s">
-        <v>176</v>
-      </c>
-      <c r="I3" s="4" t="s">
-        <v>177</v>
-      </c>
-      <c r="J3" s="4" t="s">
-        <v>178</v>
-      </c>
-      <c r="K3" s="4" t="s">
-        <v>174</v>
-      </c>
       <c r="L3" s="4" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="M3" s="4"/>
       <c r="N3" s="4"/>
@@ -4490,7 +5063,7 @@
       <c r="Y3" s="4"/>
       <c r="Z3" s="4"/>
       <c r="AA3" s="4" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="AB3" s="4"/>
       <c r="AC3" s="4"/>
@@ -4529,43 +5102,44 @@
       <c r="BJ3" s="4"/>
       <c r="BK3" s="4"/>
       <c r="BL3" s="4"/>
+      <c r="BM3" s="4"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
         <v>17</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="L4" s="4" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="M4" s="4"/>
       <c r="N4" s="4"/>
@@ -4582,7 +5156,7 @@
       <c r="Y4" s="4"/>
       <c r="Z4" s="4"/>
       <c r="AA4" s="4" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AB4" s="4"/>
       <c r="AC4" s="4"/>
@@ -4621,325 +5195,326 @@
       <c r="BJ4" s="4"/>
       <c r="BK4" s="4"/>
       <c r="BL4" s="4"/>
+      <c r="BM4" s="4"/>
     </row>
     <row r="5">
       <c r="B5" s="5" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C5" s="5">
         <v>0</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="J5" s="5" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="K5" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="L5" s="5" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AA5" s="5" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AT5" s="5" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AX5" s="5" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="BI5" s="5" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="6">
       <c r="B6" s="6" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C6" s="6">
         <v>0</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="J6" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="K6" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="L6" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AA6" s="6" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AT6" s="6" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AX6" s="6" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="BI6" s="6" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="7">
       <c r="B7" s="5" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C7" s="5">
         <v>0</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="K7" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="L7" s="5" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AA7" s="5" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AT7" s="5" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AW7" s="5" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="BI7" s="5" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="6" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C8" s="6">
         <v>0</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="J8" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="K8" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="L8" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AA8" s="6" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AT8" s="6" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AW8" s="6" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="BI8" s="6" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="9">
       <c r="B9" s="5" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C9" s="5">
         <v>0</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="K9" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="L9" s="5" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AA9" s="5" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AT9" s="5" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AW9" s="5" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="BI9" s="5" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="10">
       <c r="B10" s="6" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C10" s="6">
         <v>0</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="J10" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="K10" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="L10" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AA10" s="6" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AT10" s="6" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AW10" s="6" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="BI10" s="6" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="11">
       <c r="B11" s="5" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C11" s="5">
         <v>0</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="J11" s="5" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="K11" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="L11" s="5" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AA11" s="5" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AD11" s="5">
         <v>25</v>
@@ -4947,43 +5522,43 @@
     </row>
     <row r="12">
       <c r="B12" s="6" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C12" s="6">
         <v>0</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="J12" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="K12" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="L12" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AA12" s="6" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AT12" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AU12" s="6">
         <v>1</v>
@@ -4991,319 +5566,319 @@
     </row>
     <row r="13">
       <c r="B13" s="5" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C13" s="5">
         <v>0</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="J13" s="5" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="K13" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="L13" s="5" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AA13" s="5" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="6" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C14" s="6">
         <v>0</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="J14" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="K14" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="L14" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AA14" s="6" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AT14" s="6" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AU14" s="6">
         <v>1</v>
       </c>
       <c r="BK14" s="6" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="5" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C15" s="5">
         <v>0</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I15" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="J15" s="5" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="K15" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="L15" s="5" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AA15" s="5" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AT15" s="5" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AU15" s="5">
         <v>1</v>
       </c>
       <c r="BK15" s="5" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="16">
       <c r="B16" s="6" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C16" s="6">
         <v>0</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="J16" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="K16" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="L16" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AA16" s="6" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AT16" s="6" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AU16" s="6">
         <v>1</v>
       </c>
       <c r="BK16" s="6" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="5" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C17" s="5">
         <v>0</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I17" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="J17" s="5" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="K17" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="L17" s="5" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AA17" s="5" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AT17" s="5" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AU17" s="5">
         <v>1</v>
       </c>
       <c r="BK17" s="5" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C18" s="6">
         <v>0</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I18" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="J18" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="K18" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="L18" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AA18" s="6" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AT18" s="6" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AU18" s="6">
         <v>1</v>
       </c>
       <c r="BK18" s="6" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="5" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C19" s="5">
         <v>0</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H19" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I19" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="J19" s="5" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="K19" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="L19" s="5" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AA19" s="5" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AF19" s="5" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AG19" s="5" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AH19" s="5">
         <v>1</v>
@@ -5311,46 +5886,46 @@
     </row>
     <row r="20">
       <c r="B20" s="6" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C20" s="6">
         <v>0</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I20" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="J20" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="K20" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="L20" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AA20" s="6" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AF20" s="6" t="s">
+        <v>354</v>
+      </c>
+      <c r="AG20" s="6" t="s">
         <v>353</v>
-      </c>
-      <c r="AG20" s="6" t="s">
-        <v>352</v>
       </c>
       <c r="AH20" s="6">
         <v>1</v>
@@ -5358,219 +5933,219 @@
     </row>
     <row r="21">
       <c r="B21" s="5" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C21" s="5">
         <v>0</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H21" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I21" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="J21" s="5" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="K21" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="L21" s="5" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AA21" s="5" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AH21" s="5">
         <v>1</v>
       </c>
       <c r="BF21" s="5" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="BH21" s="5" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="22">
       <c r="B22" s="6" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C22" s="6">
         <v>0</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I22" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="J22" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="K22" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="L22" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AA22" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AH22" s="6">
         <v>1</v>
       </c>
       <c r="BF22" s="6" t="s">
+        <v>357</v>
+      </c>
+      <c r="BH22" s="6" t="s">
         <v>356</v>
-      </c>
-      <c r="BH22" s="6" t="s">
-        <v>355</v>
       </c>
     </row>
     <row r="23">
       <c r="B23" s="5" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C23" s="5">
         <v>0</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H23" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I23" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="J23" s="5" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="K23" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="L23" s="5" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AA23" s="5" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="24">
       <c r="B24" s="6" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C24" s="6">
         <v>0</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I24" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="J24" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="K24" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="L24" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AA24" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AH24" s="6">
         <v>3</v>
       </c>
       <c r="BF24" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="BH24" s="6" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="25">
       <c r="B25" s="5" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C25" s="5">
         <v>0</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H25" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I25" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="J25" s="5" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="K25" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="L25" s="5" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AA25" s="5" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AE25" s="5">
         <v>40</v>
@@ -5581,46 +6156,46 @@
     </row>
     <row r="26">
       <c r="B26" s="6" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C26" s="6">
         <v>0</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F26" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I26" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="J26" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="K26" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="L26" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AA26" s="6" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AF26" s="6" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AG26" s="6" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AH26" s="6">
         <v>5</v>
@@ -5628,43 +6203,43 @@
     </row>
     <row r="27">
       <c r="B27" s="5" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C27" s="5">
         <v>0</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H27" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I27" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="J27" s="5" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="K27" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="L27" s="5" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AA27" s="5" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AR27" s="5" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AS27" s="5">
         <v>3</v>
@@ -5672,53 +6247,5122 @@
     </row>
     <row r="28">
       <c r="B28" s="6" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C28" s="6">
         <v>0</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F28" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I28" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="J28" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="K28" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="L28" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AA28" s="6" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AT28" s="6" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AU28" s="6">
         <v>2</v>
       </c>
       <c r="AX28" s="6" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B2:BL28"/>
+  <autoFilter ref="B2:BM28"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1:E24"/>
+  <sheetFormatPr defaultColWidth="8.43" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="42.1875" customWidth="1"/>
+    <col min="2" max="2" width="53.90625" customWidth="1"/>
+    <col min="3" max="3" width="29.296875" customWidth="1"/>
+    <col min="4" max="4" width="14.0625" customWidth="1"/>
+    <col min="5" max="5" width="24.609375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>367</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>368</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="5" t="s">
+        <v>371</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>372</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>373</v>
+      </c>
+      <c r="E5" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="6" t="s">
+        <v>374</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>375</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>373</v>
+      </c>
+      <c r="E6" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="5" t="s">
+        <v>376</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>377</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>373</v>
+      </c>
+      <c r="E7" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="6" t="s">
+        <v>378</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>379</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>373</v>
+      </c>
+      <c r="E8" s="6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="5" t="s">
+        <v>380</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>381</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>373</v>
+      </c>
+      <c r="E9" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="6" t="s">
+        <v>382</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>383</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>384</v>
+      </c>
+      <c r="E10" s="6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="5" t="s">
+        <v>385</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>386</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>387</v>
+      </c>
+      <c r="E11" s="5">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="6" t="s">
+        <v>388</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>389</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>390</v>
+      </c>
+      <c r="E12" s="6">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="5" t="s">
+        <v>391</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>392</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>393</v>
+      </c>
+      <c r="E13" s="5">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="6" t="s">
+        <v>394</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>395</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>396</v>
+      </c>
+      <c r="E14" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="5" t="s">
+        <v>397</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>398</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>399</v>
+      </c>
+      <c r="E15" s="5">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="6" t="s">
+        <v>400</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>401</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>402</v>
+      </c>
+      <c r="E16" s="6">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="5" t="s">
+        <v>403</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>404</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>405</v>
+      </c>
+      <c r="E17" s="5">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="6" t="s">
+        <v>406</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>407</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>408</v>
+      </c>
+      <c r="E18" s="6">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="5" t="s">
+        <v>409</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>410</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>411</v>
+      </c>
+      <c r="E19" s="5">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="6" t="s">
+        <v>412</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>413</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>414</v>
+      </c>
+      <c r="E20" s="6">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="5" t="s">
+        <v>415</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>416</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>417</v>
+      </c>
+      <c r="E21" s="5">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="6" t="s">
+        <v>418</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>419</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>420</v>
+      </c>
+      <c r="E22" s="6">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="5" t="s">
+        <v>421</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>422</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>423</v>
+      </c>
+      <c r="E23" s="5">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="6" t="s">
+        <v>424</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>425</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>426</v>
+      </c>
+      <c r="E24" s="6">
+        <v>20</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="B2:E24"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1:BM63"/>
+  <sheetFormatPr defaultColWidth="8.43" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="50.390625" customWidth="1"/>
+    <col min="2" max="2" width="53.90625" customWidth="1"/>
+    <col min="3" max="3" width="24.609375" customWidth="1"/>
+    <col min="4" max="4" width="18.75" customWidth="1"/>
+    <col min="5" max="6" width="14.0625" customWidth="1"/>
+    <col min="7" max="7" width="17.578125" customWidth="1"/>
+    <col min="8" max="9" width="15.234375" customWidth="1"/>
+    <col min="10" max="10" width="8.203125" customWidth="1"/>
+    <col min="11" max="11" width="15.234375" customWidth="1"/>
+    <col min="12" max="12" width="19.921875" customWidth="1"/>
+    <col min="13" max="14" width="18.75" customWidth="1"/>
+    <col min="15" max="15" width="26.953125" customWidth="1"/>
+    <col min="16" max="16" width="18.75" customWidth="1"/>
+    <col min="17" max="17" width="22.265625" customWidth="1"/>
+    <col min="18" max="18" width="19.921875" customWidth="1"/>
+    <col min="19" max="19" width="25.78125" customWidth="1"/>
+    <col min="20" max="20" width="21.09375" customWidth="1"/>
+    <col min="21" max="22" width="22.265625" customWidth="1"/>
+    <col min="23" max="23" width="15.234375" customWidth="1"/>
+    <col min="24" max="24" width="22.265625" customWidth="1"/>
+    <col min="25" max="26" width="17.578125" customWidth="1"/>
+    <col min="27" max="28" width="19.921875" customWidth="1"/>
+    <col min="29" max="29" width="18.75" customWidth="1"/>
+    <col min="30" max="30" width="19.921875" customWidth="1"/>
+    <col min="31" max="31" width="17.578125" customWidth="1"/>
+    <col min="32" max="33" width="18.75" customWidth="1"/>
+    <col min="34" max="34" width="19.921875" customWidth="1"/>
+    <col min="35" max="35" width="25.78125" customWidth="1"/>
+    <col min="36" max="37" width="17.578125" customWidth="1"/>
+    <col min="38" max="38" width="19.921875" customWidth="1"/>
+    <col min="39" max="39" width="22.265625" customWidth="1"/>
+    <col min="40" max="41" width="18.75" customWidth="1"/>
+    <col min="42" max="43" width="19.921875" customWidth="1"/>
+    <col min="44" max="44" width="24.609375" customWidth="1"/>
+    <col min="45" max="46" width="21.09375" customWidth="1"/>
+    <col min="47" max="47" width="19.921875" customWidth="1"/>
+    <col min="48" max="48" width="25.78125" customWidth="1"/>
+    <col min="49" max="49" width="22.265625" customWidth="1"/>
+    <col min="50" max="50" width="21.09375" customWidth="1"/>
+    <col min="51" max="51" width="26.953125" customWidth="1"/>
+    <col min="52" max="53" width="18.75" customWidth="1"/>
+    <col min="54" max="54" width="21.09375" customWidth="1"/>
+    <col min="55" max="55" width="19.921875" customWidth="1"/>
+    <col min="56" max="56" width="21.09375" customWidth="1"/>
+    <col min="57" max="57" width="18.75" customWidth="1"/>
+    <col min="58" max="58" width="30.46875" customWidth="1"/>
+    <col min="59" max="60" width="23.4375" customWidth="1"/>
+    <col min="61" max="61" width="18.75" customWidth="1"/>
+    <col min="62" max="63" width="21.09375" customWidth="1"/>
+    <col min="64" max="65" width="22.265625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
+      <c r="M1" s="2"/>
+      <c r="N1" s="2"/>
+      <c r="O1" s="2"/>
+      <c r="P1" s="2"/>
+      <c r="Q1" s="2"/>
+      <c r="R1" s="2"/>
+      <c r="S1" s="2"/>
+      <c r="T1" s="2"/>
+      <c r="U1" s="2"/>
+      <c r="V1" s="2"/>
+      <c r="W1" s="2"/>
+      <c r="X1" s="2"/>
+      <c r="Y1" s="2"/>
+      <c r="Z1" s="2"/>
+      <c r="AA1" s="2"/>
+      <c r="AB1" s="2"/>
+      <c r="AC1" s="2"/>
+      <c r="AD1" s="2"/>
+      <c r="AE1" s="2"/>
+      <c r="AF1" s="2"/>
+      <c r="AG1" s="2"/>
+      <c r="AH1" s="2"/>
+      <c r="AI1" s="2"/>
+      <c r="AJ1" s="2"/>
+      <c r="AK1" s="2"/>
+      <c r="AL1" s="2"/>
+      <c r="AM1" s="2"/>
+      <c r="AN1" s="2"/>
+      <c r="AO1" s="2"/>
+      <c r="AP1" s="2"/>
+      <c r="AQ1" s="2"/>
+      <c r="AR1" s="2"/>
+      <c r="AS1" s="2"/>
+      <c r="AT1" s="2"/>
+      <c r="AU1" s="2"/>
+      <c r="AV1" s="2"/>
+      <c r="AW1" s="2"/>
+      <c r="AX1" s="2"/>
+      <c r="AY1" s="2"/>
+      <c r="AZ1" s="2"/>
+      <c r="BA1" s="2"/>
+      <c r="BB1" s="2"/>
+      <c r="BC1" s="2"/>
+      <c r="BD1" s="2"/>
+      <c r="BE1" s="2"/>
+      <c r="BF1" s="2"/>
+      <c r="BG1" s="2"/>
+      <c r="BH1" s="2"/>
+      <c r="BI1" s="2"/>
+      <c r="BJ1" s="2"/>
+      <c r="BK1" s="2"/>
+      <c r="BL1" s="2"/>
+      <c r="BM1" s="2"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="L2" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="M2" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="N2" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="O2" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="P2" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="Q2" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="R2" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="S2" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="T2" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="U2" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="V2" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="W2" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="X2" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="Y2" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="Z2" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="AA2" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="AB2" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="AC2" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="AD2" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="AE2" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="AF2" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="AG2" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="AH2" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="AI2" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="AJ2" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="AK2" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="AL2" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="AM2" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="AN2" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="AO2" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="AP2" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="AQ2" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="AR2" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="AS2" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="AT2" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="AU2" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="AV2" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="AW2" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="AX2" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="AY2" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="AZ2" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="BA2" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="BB2" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="BC2" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="BD2" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="BE2" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="BF2" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="BG2" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="BH2" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="BI2" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="BJ2" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="BK2" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="BL2" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="BM2" s="4" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>429</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="K3" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="L3" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="M3" s="4"/>
+      <c r="N3" s="4"/>
+      <c r="O3" s="4"/>
+      <c r="P3" s="4"/>
+      <c r="Q3" s="4"/>
+      <c r="R3" s="4"/>
+      <c r="S3" s="4"/>
+      <c r="T3" s="4"/>
+      <c r="U3" s="4"/>
+      <c r="V3" s="4"/>
+      <c r="W3" s="4"/>
+      <c r="X3" s="4"/>
+      <c r="Y3" s="4"/>
+      <c r="Z3" s="4"/>
+      <c r="AA3" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="AB3" s="4"/>
+      <c r="AC3" s="4"/>
+      <c r="AD3" s="4"/>
+      <c r="AE3" s="4"/>
+      <c r="AF3" s="4"/>
+      <c r="AG3" s="4"/>
+      <c r="AH3" s="4"/>
+      <c r="AI3" s="4"/>
+      <c r="AJ3" s="4"/>
+      <c r="AK3" s="4"/>
+      <c r="AL3" s="4"/>
+      <c r="AM3" s="4"/>
+      <c r="AN3" s="4"/>
+      <c r="AO3" s="4"/>
+      <c r="AP3" s="4"/>
+      <c r="AQ3" s="4"/>
+      <c r="AR3" s="4"/>
+      <c r="AS3" s="4"/>
+      <c r="AT3" s="4"/>
+      <c r="AU3" s="4"/>
+      <c r="AV3" s="4"/>
+      <c r="AW3" s="4"/>
+      <c r="AX3" s="4"/>
+      <c r="AY3" s="4"/>
+      <c r="AZ3" s="4"/>
+      <c r="BA3" s="4"/>
+      <c r="BB3" s="4"/>
+      <c r="BC3" s="4"/>
+      <c r="BD3" s="4"/>
+      <c r="BE3" s="4"/>
+      <c r="BF3" s="4"/>
+      <c r="BG3" s="4"/>
+      <c r="BH3" s="4"/>
+      <c r="BI3" s="4"/>
+      <c r="BJ3" s="4"/>
+      <c r="BK3" s="4"/>
+      <c r="BL3" s="4"/>
+      <c r="BM3" s="4"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="K4" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="L4" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="M4" s="4"/>
+      <c r="N4" s="4"/>
+      <c r="O4" s="4"/>
+      <c r="P4" s="4"/>
+      <c r="Q4" s="4"/>
+      <c r="R4" s="4"/>
+      <c r="S4" s="4"/>
+      <c r="T4" s="4"/>
+      <c r="U4" s="4"/>
+      <c r="V4" s="4"/>
+      <c r="W4" s="4"/>
+      <c r="X4" s="4"/>
+      <c r="Y4" s="4"/>
+      <c r="Z4" s="4"/>
+      <c r="AA4" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="AB4" s="4"/>
+      <c r="AC4" s="4"/>
+      <c r="AD4" s="4"/>
+      <c r="AE4" s="4"/>
+      <c r="AF4" s="4"/>
+      <c r="AG4" s="4"/>
+      <c r="AH4" s="4"/>
+      <c r="AI4" s="4"/>
+      <c r="AJ4" s="4"/>
+      <c r="AK4" s="4"/>
+      <c r="AL4" s="4"/>
+      <c r="AM4" s="4"/>
+      <c r="AN4" s="4"/>
+      <c r="AO4" s="4"/>
+      <c r="AP4" s="4"/>
+      <c r="AQ4" s="4"/>
+      <c r="AR4" s="4"/>
+      <c r="AS4" s="4"/>
+      <c r="AT4" s="4"/>
+      <c r="AU4" s="4"/>
+      <c r="AV4" s="4"/>
+      <c r="AW4" s="4"/>
+      <c r="AX4" s="4"/>
+      <c r="AY4" s="4"/>
+      <c r="AZ4" s="4"/>
+      <c r="BA4" s="4"/>
+      <c r="BB4" s="4"/>
+      <c r="BC4" s="4"/>
+      <c r="BD4" s="4"/>
+      <c r="BE4" s="4"/>
+      <c r="BF4" s="4"/>
+      <c r="BG4" s="4"/>
+      <c r="BH4" s="4"/>
+      <c r="BI4" s="4"/>
+      <c r="BJ4" s="4"/>
+      <c r="BK4" s="4"/>
+      <c r="BL4" s="4"/>
+      <c r="BM4" s="4"/>
+    </row>
+    <row r="5">
+      <c r="B5" s="5" t="s">
+        <v>371</v>
+      </c>
+      <c r="C5" s="5">
+        <v>0</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="J5" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="K5" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="L5" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="AA5" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="AH5" s="5">
+        <v>1</v>
+      </c>
+      <c r="BF5" s="5" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="6" t="s">
+        <v>371</v>
+      </c>
+      <c r="C6" s="6">
+        <v>1</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="H6" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="I6" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="J6" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="K6" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="L6" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="AA6" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="AH6" s="6">
+        <v>1</v>
+      </c>
+      <c r="BF6" s="6" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="5" t="s">
+        <v>371</v>
+      </c>
+      <c r="C7" s="5">
+        <v>2</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="I7" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="J7" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="K7" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="L7" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="AA7" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="AH7" s="5">
+        <v>1</v>
+      </c>
+      <c r="BF7" s="5" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="6" t="s">
+        <v>371</v>
+      </c>
+      <c r="C8" s="6">
+        <v>3</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="H8" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="I8" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="J8" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="K8" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="L8" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="AA8" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="AH8" s="6">
+        <v>0</v>
+      </c>
+      <c r="BF8" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="BG8" s="6" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="5" t="s">
+        <v>371</v>
+      </c>
+      <c r="C9" s="5">
+        <v>4</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="H9" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="I9" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="J9" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="K9" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="L9" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="AA9" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="AH9" s="5">
+        <v>1</v>
+      </c>
+      <c r="BF9" s="5" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="6" t="s">
+        <v>371</v>
+      </c>
+      <c r="C10" s="6">
+        <v>5</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="G10" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="H10" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="I10" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="J10" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="K10" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="L10" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="AA10" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="AT10" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="AU10" s="6">
+        <v>5</v>
+      </c>
+      <c r="BK10" s="6" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="5" t="s">
+        <v>374</v>
+      </c>
+      <c r="C11" s="5">
+        <v>0</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="H11" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="I11" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="J11" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="K11" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="L11" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="AA11" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="AT11" s="5" t="s">
+        <v>333</v>
+      </c>
+      <c r="AU11" s="5">
+        <v>1</v>
+      </c>
+      <c r="BK11" s="5" t="s">
+        <v>434</v>
+      </c>
+      <c r="BM11" s="5" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="6" t="s">
+        <v>374</v>
+      </c>
+      <c r="C12" s="6">
+        <v>1</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="G12" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="H12" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="I12" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="J12" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="K12" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="L12" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="AA12" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="AT12" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="AU12" s="6">
+        <v>1</v>
+      </c>
+      <c r="BK12" s="6" t="s">
+        <v>435</v>
+      </c>
+      <c r="BM12" s="6" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="5" t="s">
+        <v>376</v>
+      </c>
+      <c r="C13" s="5">
+        <v>0</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="H13" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="I13" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="J13" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="K13" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="L13" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="AA13" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="AH13" s="5">
+        <v>100</v>
+      </c>
+      <c r="BF13" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="BG13" s="5" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="6" t="s">
+        <v>376</v>
+      </c>
+      <c r="C14" s="6">
+        <v>1</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="G14" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="H14" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="I14" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="J14" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="K14" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="L14" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="AA14" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="AH14" s="6">
+        <v>1</v>
+      </c>
+      <c r="BF14" s="6" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="5" t="s">
+        <v>376</v>
+      </c>
+      <c r="C15" s="5">
+        <v>2</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="G15" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="H15" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="I15" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="J15" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="K15" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="L15" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="AA15" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="AT15" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="AU15" s="5">
+        <v>1</v>
+      </c>
+      <c r="BK15" s="5" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="6" t="s">
+        <v>376</v>
+      </c>
+      <c r="C16" s="6">
+        <v>3</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="F16" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="G16" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="H16" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="I16" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="J16" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="K16" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="L16" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="AA16" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="AT16" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="AU16" s="6">
+        <v>1</v>
+      </c>
+      <c r="BK16" s="6" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="C17" s="5">
+        <v>0</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="G17" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="H17" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="I17" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="J17" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="K17" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="L17" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="AA17" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="AH17" s="5">
+        <v>1</v>
+      </c>
+      <c r="BF17" s="5" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="6" t="s">
+        <v>378</v>
+      </c>
+      <c r="C18" s="6">
+        <v>1</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="G18" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="H18" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="I18" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="J18" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="K18" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="L18" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="AA18" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="AT18" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="AU18" s="6">
+        <v>1</v>
+      </c>
+      <c r="BK18" s="6" t="s">
+        <v>440</v>
+      </c>
+      <c r="BM18" s="6" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="5" t="s">
+        <v>380</v>
+      </c>
+      <c r="C19" s="5">
+        <v>0</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="G19" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="H19" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="I19" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="J19" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="K19" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="L19" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="AA19" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="AH19" s="5">
+        <v>4</v>
+      </c>
+      <c r="BF19" s="5" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="6" t="s">
+        <v>382</v>
+      </c>
+      <c r="C20" s="6">
+        <v>0</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="F20" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="G20" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="H20" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="I20" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="J20" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="K20" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="L20" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="AA20" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="AH20" s="6">
+        <v>0</v>
+      </c>
+      <c r="BF20" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="BG20" s="6" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="5" t="s">
+        <v>382</v>
+      </c>
+      <c r="C21" s="5">
+        <v>1</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="G21" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="H21" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="I21" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="J21" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="K21" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="L21" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="AA21" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="AH21" s="5">
+        <v>1</v>
+      </c>
+      <c r="BF21" s="5" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="6" t="s">
+        <v>382</v>
+      </c>
+      <c r="C22" s="6">
+        <v>2</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="F22" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="G22" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="H22" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="I22" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="J22" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="K22" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="L22" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="AA22" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="AT22" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="AU22" s="6">
+        <v>1</v>
+      </c>
+      <c r="AW22" s="6" t="s">
+        <v>336</v>
+      </c>
+      <c r="BK22" s="6" t="s">
+        <v>442</v>
+      </c>
+      <c r="BM22" s="6" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="5" t="s">
+        <v>382</v>
+      </c>
+      <c r="C23" s="5">
+        <v>3</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="F23" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="G23" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="H23" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="I23" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="J23" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="K23" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="L23" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="AA23" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="AT23" s="5" t="s">
+        <v>333</v>
+      </c>
+      <c r="AU23" s="5">
+        <v>1</v>
+      </c>
+      <c r="BK23" s="5" t="s">
+        <v>443</v>
+      </c>
+      <c r="BM23" s="5" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="6" t="s">
+        <v>385</v>
+      </c>
+      <c r="C24" s="6">
+        <v>0</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="F24" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="G24" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="H24" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="I24" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="J24" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="K24" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="L24" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="AA24" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="AH24" s="6">
+        <v>10</v>
+      </c>
+      <c r="BF24" s="6" t="s">
+        <v>223</v>
+      </c>
+      <c r="BG24" s="6" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="5" t="s">
+        <v>385</v>
+      </c>
+      <c r="C25" s="5">
+        <v>1</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="F25" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="G25" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="H25" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="I25" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="J25" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="K25" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="L25" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="AA25" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="AH25" s="5">
+        <v>5</v>
+      </c>
+      <c r="BF25" s="5" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="6" t="s">
+        <v>388</v>
+      </c>
+      <c r="C26" s="6">
+        <v>0</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="E26" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="F26" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="G26" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="H26" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="I26" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="J26" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="K26" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="L26" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="AA26" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="AH26" s="6">
+        <v>1</v>
+      </c>
+      <c r="BF26" s="6" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="5" t="s">
+        <v>391</v>
+      </c>
+      <c r="C27" s="5">
+        <v>0</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="E27" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="F27" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="G27" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="H27" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="I27" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="J27" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="K27" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="L27" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="AA27" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="AT27" s="5" t="s">
+        <v>333</v>
+      </c>
+      <c r="AU27" s="5">
+        <v>1</v>
+      </c>
+      <c r="BK27" s="5" t="s">
+        <v>446</v>
+      </c>
+      <c r="BM27" s="5" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="6" t="s">
+        <v>394</v>
+      </c>
+      <c r="C28" s="6">
+        <v>0</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="E28" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="F28" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="G28" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="H28" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="I28" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="J28" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="K28" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="L28" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="AA28" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="AH28" s="6">
+        <v>1</v>
+      </c>
+      <c r="BF28" s="6" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="5" t="s">
+        <v>397</v>
+      </c>
+      <c r="C29" s="5">
+        <v>0</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>340</v>
+      </c>
+      <c r="E29" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="F29" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="G29" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="H29" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="I29" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="J29" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="K29" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="L29" s="5" t="s">
+        <v>448</v>
+      </c>
+      <c r="W29" s="5">
+        <v>4</v>
+      </c>
+      <c r="AA29" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="AH29" s="5">
+        <v>1</v>
+      </c>
+      <c r="BF29" s="5" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="6" t="s">
+        <v>397</v>
+      </c>
+      <c r="C30" s="6">
+        <v>1</v>
+      </c>
+      <c r="D30" s="6" t="s">
+        <v>340</v>
+      </c>
+      <c r="E30" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="F30" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="G30" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="H30" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="I30" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="J30" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="K30" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="L30" s="6" t="s">
+        <v>448</v>
+      </c>
+      <c r="W30" s="6">
+        <v>4</v>
+      </c>
+      <c r="AA30" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="AH30" s="6">
+        <v>0</v>
+      </c>
+      <c r="BF30" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="BG30" s="6" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="5" t="s">
+        <v>400</v>
+      </c>
+      <c r="C31" s="5">
+        <v>0</v>
+      </c>
+      <c r="D31" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="E31" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="F31" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="G31" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="H31" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="I31" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="J31" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="K31" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="L31" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="AA31" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="AH31" s="5">
+        <v>1</v>
+      </c>
+      <c r="BF31" s="5" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="6" t="s">
+        <v>400</v>
+      </c>
+      <c r="C32" s="6">
+        <v>1</v>
+      </c>
+      <c r="D32" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="E32" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="F32" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="G32" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="H32" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="I32" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="J32" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="K32" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="L32" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="AA32" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="AT32" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="AU32" s="6">
+        <v>1</v>
+      </c>
+      <c r="BK32" s="6" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="5" t="s">
+        <v>403</v>
+      </c>
+      <c r="C33" s="5">
+        <v>0</v>
+      </c>
+      <c r="D33" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="E33" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="F33" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="G33" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="H33" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="I33" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="J33" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="K33" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="L33" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="AA33" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="AH33" s="5">
+        <v>1</v>
+      </c>
+      <c r="BF33" s="5" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" s="6" t="s">
+        <v>403</v>
+      </c>
+      <c r="C34" s="6">
+        <v>1</v>
+      </c>
+      <c r="D34" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="E34" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="F34" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="G34" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="H34" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="I34" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="J34" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="K34" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="L34" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="AA34" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="AT34" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="AU34" s="6">
+        <v>1</v>
+      </c>
+      <c r="BK34" s="6" t="s">
+        <v>452</v>
+      </c>
+      <c r="BM34" s="6" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="5" t="s">
+        <v>403</v>
+      </c>
+      <c r="C35" s="5">
+        <v>2</v>
+      </c>
+      <c r="D35" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="E35" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="F35" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="G35" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="H35" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="I35" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="J35" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="K35" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="L35" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="AA35" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="AT35" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="AU35" s="5">
+        <v>1</v>
+      </c>
+      <c r="BK35" s="5" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="6" t="s">
+        <v>403</v>
+      </c>
+      <c r="C36" s="6">
+        <v>3</v>
+      </c>
+      <c r="D36" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="E36" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="F36" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="G36" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="H36" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="I36" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="J36" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="K36" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="L36" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="AA36" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="AT36" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="AU36" s="6">
+        <v>1</v>
+      </c>
+      <c r="BK36" s="6" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" s="5" t="s">
+        <v>403</v>
+      </c>
+      <c r="C37" s="5">
+        <v>4</v>
+      </c>
+      <c r="D37" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="E37" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="F37" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="G37" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="H37" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="I37" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="J37" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="K37" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="L37" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="AA37" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="AT37" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="AU37" s="5">
+        <v>1</v>
+      </c>
+      <c r="BK37" s="5" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="6" t="s">
+        <v>403</v>
+      </c>
+      <c r="C38" s="6">
+        <v>5</v>
+      </c>
+      <c r="D38" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="E38" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="F38" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="G38" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="H38" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="I38" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="J38" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="K38" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="L38" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="AA38" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="AT38" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="AU38" s="6">
+        <v>1</v>
+      </c>
+      <c r="BK38" s="6" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="5" t="s">
+        <v>406</v>
+      </c>
+      <c r="C39" s="5">
+        <v>0</v>
+      </c>
+      <c r="D39" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="E39" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="F39" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="G39" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="H39" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="I39" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="J39" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="K39" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="L39" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="AA39" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="AT39" s="5" t="s">
+        <v>333</v>
+      </c>
+      <c r="AU39" s="5">
+        <v>2</v>
+      </c>
+      <c r="AW39" s="5" t="s">
+        <v>336</v>
+      </c>
+      <c r="BK39" s="5" t="s">
+        <v>457</v>
+      </c>
+      <c r="BM39" s="5" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" s="6" t="s">
+        <v>409</v>
+      </c>
+      <c r="C40" s="6">
+        <v>0</v>
+      </c>
+      <c r="D40" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="E40" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="F40" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="G40" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="H40" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="I40" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="J40" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="K40" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="L40" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="AA40" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="AT40" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="AU40" s="6">
+        <v>1</v>
+      </c>
+      <c r="BK40" s="6" t="s">
+        <v>458</v>
+      </c>
+      <c r="BM40" s="6" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" s="5" t="s">
+        <v>409</v>
+      </c>
+      <c r="C41" s="5">
+        <v>1</v>
+      </c>
+      <c r="D41" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="E41" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="F41" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="G41" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="H41" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="I41" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="J41" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="K41" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="L41" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="AA41" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="AT41" s="5" t="s">
+        <v>333</v>
+      </c>
+      <c r="AU41" s="5">
+        <v>1</v>
+      </c>
+      <c r="AW41" s="5" t="s">
+        <v>336</v>
+      </c>
+      <c r="BK41" s="5" t="s">
+        <v>446</v>
+      </c>
+      <c r="BM41" s="5" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" s="6" t="s">
+        <v>412</v>
+      </c>
+      <c r="C42" s="6">
+        <v>0</v>
+      </c>
+      <c r="D42" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="E42" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="F42" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="G42" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="H42" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="I42" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="J42" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="K42" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="L42" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="AA42" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="AH42" s="6">
+        <v>2</v>
+      </c>
+      <c r="BF42" s="6" t="s">
+        <v>200</v>
+      </c>
+      <c r="BG42" s="6" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" s="5" t="s">
+        <v>412</v>
+      </c>
+      <c r="C43" s="5">
+        <v>1</v>
+      </c>
+      <c r="D43" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="E43" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="F43" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="G43" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="H43" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="I43" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="J43" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="K43" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="L43" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="AA43" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="AH43" s="5">
+        <v>2</v>
+      </c>
+      <c r="BF43" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="BG43" s="5" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" s="6" t="s">
+        <v>412</v>
+      </c>
+      <c r="C44" s="6">
+        <v>2</v>
+      </c>
+      <c r="D44" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="E44" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="F44" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="G44" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="H44" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="I44" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="J44" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="K44" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="L44" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="AA44" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="AH44" s="6">
+        <v>4</v>
+      </c>
+      <c r="BF44" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="BG44" s="6" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" s="5" t="s">
+        <v>412</v>
+      </c>
+      <c r="C45" s="5">
+        <v>3</v>
+      </c>
+      <c r="D45" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="E45" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="F45" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="G45" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="H45" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="I45" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="J45" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="K45" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="L45" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="AA45" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="AT45" s="5" t="s">
+        <v>333</v>
+      </c>
+      <c r="AU45" s="5">
+        <v>1</v>
+      </c>
+      <c r="BK45" s="5" t="s">
+        <v>459</v>
+      </c>
+      <c r="BM45" s="5" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" s="6" t="s">
+        <v>412</v>
+      </c>
+      <c r="C46" s="6">
+        <v>4</v>
+      </c>
+      <c r="D46" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="E46" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="F46" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="G46" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="H46" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="I46" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="J46" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="K46" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="L46" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="AA46" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="AT46" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="AU46" s="6">
+        <v>1</v>
+      </c>
+      <c r="BK46" s="6" t="s">
+        <v>460</v>
+      </c>
+      <c r="BM46" s="6" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" s="5" t="s">
+        <v>412</v>
+      </c>
+      <c r="C47" s="5">
+        <v>5</v>
+      </c>
+      <c r="D47" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="E47" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="F47" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="G47" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="H47" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="I47" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="J47" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="K47" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="L47" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="AA47" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="AT47" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="AU47" s="5">
+        <v>1</v>
+      </c>
+      <c r="BK47" s="5" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" s="6" t="s">
+        <v>412</v>
+      </c>
+      <c r="C48" s="6">
+        <v>6</v>
+      </c>
+      <c r="D48" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="E48" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="F48" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="G48" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="H48" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="I48" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="J48" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="K48" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="L48" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="AA48" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="AT48" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="AU48" s="6">
+        <v>1</v>
+      </c>
+      <c r="BK48" s="6" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" s="5" t="s">
+        <v>415</v>
+      </c>
+      <c r="C49" s="5">
+        <v>0</v>
+      </c>
+      <c r="D49" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="E49" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="F49" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="G49" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="H49" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="I49" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="J49" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="K49" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="L49" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="AA49" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="AH49" s="5">
+        <v>5</v>
+      </c>
+      <c r="BF49" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="BG49" s="5" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" s="6" t="s">
+        <v>415</v>
+      </c>
+      <c r="C50" s="6">
+        <v>1</v>
+      </c>
+      <c r="D50" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="E50" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="F50" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="G50" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="H50" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="I50" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="J50" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="K50" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="L50" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="AA50" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="AH50" s="6">
+        <v>6</v>
+      </c>
+      <c r="BF50" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="BG50" s="6" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" s="5" t="s">
+        <v>415</v>
+      </c>
+      <c r="C51" s="5">
+        <v>2</v>
+      </c>
+      <c r="D51" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="E51" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="F51" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="G51" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="H51" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="I51" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="J51" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="K51" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="L51" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="AA51" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="AH51" s="5">
+        <v>7</v>
+      </c>
+      <c r="BF51" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="BG51" s="5" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" s="6" t="s">
+        <v>415</v>
+      </c>
+      <c r="C52" s="6">
+        <v>3</v>
+      </c>
+      <c r="D52" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="E52" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="F52" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="G52" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="H52" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="I52" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="J52" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="K52" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="L52" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="AA52" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="AT52" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="AU52" s="6">
+        <v>1</v>
+      </c>
+      <c r="BK52" s="6" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" s="5" t="s">
+        <v>415</v>
+      </c>
+      <c r="C53" s="5">
+        <v>4</v>
+      </c>
+      <c r="D53" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="E53" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="F53" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="G53" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="H53" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="I53" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="J53" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="K53" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="L53" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="AA53" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="AT53" s="5" t="s">
+        <v>333</v>
+      </c>
+      <c r="AU53" s="5">
+        <v>1</v>
+      </c>
+      <c r="BK53" s="5" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" s="6" t="s">
+        <v>418</v>
+      </c>
+      <c r="C54" s="6">
+        <v>0</v>
+      </c>
+      <c r="D54" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="E54" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="F54" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="G54" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="H54" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="I54" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="J54" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="K54" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="L54" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="AA54" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="AH54" s="6">
+        <v>10</v>
+      </c>
+      <c r="BF54" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="BG54" s="6" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" s="5" t="s">
+        <v>418</v>
+      </c>
+      <c r="C55" s="5">
+        <v>1</v>
+      </c>
+      <c r="D55" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="E55" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="F55" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="G55" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="H55" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="I55" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="J55" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="K55" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="L55" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="AA55" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="AH55" s="5">
+        <v>1</v>
+      </c>
+      <c r="BF55" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="BG55" s="5" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" s="6" t="s">
+        <v>418</v>
+      </c>
+      <c r="C56" s="6">
+        <v>2</v>
+      </c>
+      <c r="D56" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="E56" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="F56" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="G56" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="H56" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="I56" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="J56" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="K56" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="L56" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="AA56" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="AH56" s="6">
+        <v>6</v>
+      </c>
+      <c r="BF56" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="BG56" s="6" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" s="5" t="s">
+        <v>418</v>
+      </c>
+      <c r="C57" s="5">
+        <v>3</v>
+      </c>
+      <c r="D57" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="E57" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="F57" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="G57" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="H57" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="I57" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="J57" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="K57" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="L57" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="AA57" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="AH57" s="5">
+        <v>1</v>
+      </c>
+      <c r="BF57" s="5" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="B58" s="6" t="s">
+        <v>418</v>
+      </c>
+      <c r="C58" s="6">
+        <v>4</v>
+      </c>
+      <c r="D58" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="E58" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="F58" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="G58" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="H58" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="I58" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="J58" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="K58" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="L58" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="AA58" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="AT58" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="AU58" s="6">
+        <v>1</v>
+      </c>
+      <c r="BK58" s="6" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59" s="5" t="s">
+        <v>421</v>
+      </c>
+      <c r="C59" s="5">
+        <v>0</v>
+      </c>
+      <c r="D59" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="E59" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="F59" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="G59" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="H59" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="I59" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="J59" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="K59" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="L59" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="AA59" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="AH59" s="5">
+        <v>3</v>
+      </c>
+      <c r="BF59" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="BG59" s="5" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" s="6" t="s">
+        <v>421</v>
+      </c>
+      <c r="C60" s="6">
+        <v>1</v>
+      </c>
+      <c r="D60" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="E60" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="F60" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="G60" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="H60" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="I60" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="J60" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="K60" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="L60" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="AA60" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="AH60" s="6">
+        <v>1</v>
+      </c>
+      <c r="BF60" s="6" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="B61" s="5" t="s">
+        <v>421</v>
+      </c>
+      <c r="C61" s="5">
+        <v>2</v>
+      </c>
+      <c r="D61" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="E61" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="F61" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="G61" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="H61" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="I61" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="J61" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="K61" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="L61" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="AA61" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="AH61" s="5">
+        <v>1</v>
+      </c>
+      <c r="BF61" s="5" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62" s="6" t="s">
+        <v>424</v>
+      </c>
+      <c r="C62" s="6">
+        <v>0</v>
+      </c>
+      <c r="D62" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="E62" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="F62" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="G62" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="H62" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="I62" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="J62" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="K62" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="L62" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="AA62" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="AH62" s="6">
+        <v>0</v>
+      </c>
+      <c r="BF62" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="BG62" s="6" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" s="5" t="s">
+        <v>424</v>
+      </c>
+      <c r="C63" s="5">
+        <v>1</v>
+      </c>
+      <c r="D63" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="E63" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="F63" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="G63" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="H63" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="I63" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="J63" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="K63" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="L63" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="AA63" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="AH63" s="5">
+        <v>1</v>
+      </c>
+      <c r="BF63" s="5" t="s">
+        <v>451</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="B2:BM63"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1:E78"/>
+  <sheetFormatPr defaultColWidth="8.43" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="46.875" customWidth="1"/>
+    <col min="2" max="2" width="49.21875" customWidth="1"/>
+    <col min="3" max="3" width="24.609375" customWidth="1"/>
+    <col min="4" max="4" width="11.71875" customWidth="1"/>
+    <col min="5" max="5" width="25.78125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>466</v>
+      </c>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>467</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>429</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>469</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>470</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>472</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="5" t="s">
+        <v>371</v>
+      </c>
+      <c r="C5" s="5">
+        <v>0</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>333</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="6" t="s">
+        <v>371</v>
+      </c>
+      <c r="C6" s="6">
+        <v>1</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="5" t="s">
+        <v>371</v>
+      </c>
+      <c r="C7" s="5">
+        <v>2</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>333</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="6" t="s">
+        <v>371</v>
+      </c>
+      <c r="C8" s="6">
+        <v>3</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="5" t="s">
+        <v>371</v>
+      </c>
+      <c r="C9" s="5">
+        <v>4</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="6" t="s">
+        <v>371</v>
+      </c>
+      <c r="C10" s="6">
+        <v>5</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="5" t="s">
+        <v>382</v>
+      </c>
+      <c r="C11" s="5">
+        <v>0</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>477</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="6" t="s">
+        <v>388</v>
+      </c>
+      <c r="C12" s="6">
+        <v>0</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="5" t="s">
+        <v>388</v>
+      </c>
+      <c r="C13" s="5">
+        <v>1</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>333</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="6" t="s">
+        <v>388</v>
+      </c>
+      <c r="C14" s="6">
+        <v>2</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="5" t="s">
+        <v>388</v>
+      </c>
+      <c r="C15" s="5">
+        <v>3</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>333</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="6" t="s">
+        <v>388</v>
+      </c>
+      <c r="C16" s="6">
+        <v>4</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="5" t="s">
+        <v>388</v>
+      </c>
+      <c r="C17" s="5">
+        <v>5</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>333</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="6" t="s">
+        <v>388</v>
+      </c>
+      <c r="C18" s="6">
+        <v>6</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="5" t="s">
+        <v>388</v>
+      </c>
+      <c r="C19" s="5">
+        <v>7</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>333</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="6" t="s">
+        <v>388</v>
+      </c>
+      <c r="C20" s="6">
+        <v>8</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="5" t="s">
+        <v>388</v>
+      </c>
+      <c r="C21" s="5">
+        <v>9</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>333</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="6" t="s">
+        <v>388</v>
+      </c>
+      <c r="C22" s="6">
+        <v>10</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="5" t="s">
+        <v>388</v>
+      </c>
+      <c r="C23" s="5">
+        <v>11</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>477</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="6" t="s">
+        <v>397</v>
+      </c>
+      <c r="C24" s="6">
+        <v>0</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>477</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="5" t="s">
+        <v>400</v>
+      </c>
+      <c r="C25" s="5">
+        <v>0</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="6" t="s">
+        <v>400</v>
+      </c>
+      <c r="C26" s="6">
+        <v>1</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="E26" s="6" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="5" t="s">
+        <v>406</v>
+      </c>
+      <c r="C27" s="5">
+        <v>0</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>333</v>
+      </c>
+      <c r="E27" s="5" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="6" t="s">
+        <v>406</v>
+      </c>
+      <c r="C28" s="6">
+        <v>1</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="E28" s="6" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="5" t="s">
+        <v>406</v>
+      </c>
+      <c r="C29" s="5">
+        <v>2</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>333</v>
+      </c>
+      <c r="E29" s="5" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="6" t="s">
+        <v>406</v>
+      </c>
+      <c r="C30" s="6">
+        <v>3</v>
+      </c>
+      <c r="D30" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="E30" s="6" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="5" t="s">
+        <v>406</v>
+      </c>
+      <c r="C31" s="5">
+        <v>4</v>
+      </c>
+      <c r="D31" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="E31" s="5" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="6" t="s">
+        <v>406</v>
+      </c>
+      <c r="C32" s="6">
+        <v>5</v>
+      </c>
+      <c r="D32" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="E32" s="6" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="5" t="s">
+        <v>406</v>
+      </c>
+      <c r="C33" s="5">
+        <v>6</v>
+      </c>
+      <c r="D33" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="E33" s="5" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" s="6" t="s">
+        <v>406</v>
+      </c>
+      <c r="C34" s="6">
+        <v>7</v>
+      </c>
+      <c r="D34" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="E34" s="6" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="5" t="s">
+        <v>406</v>
+      </c>
+      <c r="C35" s="5">
+        <v>8</v>
+      </c>
+      <c r="D35" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="E35" s="5" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="6" t="s">
+        <v>406</v>
+      </c>
+      <c r="C36" s="6">
+        <v>9</v>
+      </c>
+      <c r="D36" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="E36" s="6" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" s="5" t="s">
+        <v>406</v>
+      </c>
+      <c r="C37" s="5">
+        <v>10</v>
+      </c>
+      <c r="D37" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="E37" s="5" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="6" t="s">
+        <v>406</v>
+      </c>
+      <c r="C38" s="6">
+        <v>11</v>
+      </c>
+      <c r="D38" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="E38" s="6" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="5" t="s">
+        <v>406</v>
+      </c>
+      <c r="C39" s="5">
+        <v>12</v>
+      </c>
+      <c r="D39" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="E39" s="5" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" s="6" t="s">
+        <v>406</v>
+      </c>
+      <c r="C40" s="6">
+        <v>13</v>
+      </c>
+      <c r="D40" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="E40" s="6" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" s="5" t="s">
+        <v>406</v>
+      </c>
+      <c r="C41" s="5">
+        <v>14</v>
+      </c>
+      <c r="D41" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="E41" s="5" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" s="6" t="s">
+        <v>406</v>
+      </c>
+      <c r="C42" s="6">
+        <v>15</v>
+      </c>
+      <c r="D42" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="E42" s="6" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" s="5" t="s">
+        <v>406</v>
+      </c>
+      <c r="C43" s="5">
+        <v>16</v>
+      </c>
+      <c r="D43" s="5" t="s">
+        <v>345</v>
+      </c>
+      <c r="E43" s="5" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" s="6" t="s">
+        <v>406</v>
+      </c>
+      <c r="C44" s="6">
+        <v>17</v>
+      </c>
+      <c r="D44" s="6" t="s">
+        <v>345</v>
+      </c>
+      <c r="E44" s="6" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" s="5" t="s">
+        <v>406</v>
+      </c>
+      <c r="C45" s="5">
+        <v>18</v>
+      </c>
+      <c r="D45" s="5" t="s">
+        <v>345</v>
+      </c>
+      <c r="E45" s="5" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" s="6" t="s">
+        <v>406</v>
+      </c>
+      <c r="C46" s="6">
+        <v>19</v>
+      </c>
+      <c r="D46" s="6" t="s">
+        <v>506</v>
+      </c>
+      <c r="E46" s="6" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" s="5" t="s">
+        <v>412</v>
+      </c>
+      <c r="C47" s="5">
+        <v>0</v>
+      </c>
+      <c r="D47" s="5" t="s">
+        <v>333</v>
+      </c>
+      <c r="E47" s="5" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" s="6" t="s">
+        <v>412</v>
+      </c>
+      <c r="C48" s="6">
+        <v>1</v>
+      </c>
+      <c r="D48" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="E48" s="6" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" s="5" t="s">
+        <v>412</v>
+      </c>
+      <c r="C49" s="5">
+        <v>2</v>
+      </c>
+      <c r="D49" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="E49" s="5" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" s="6" t="s">
+        <v>415</v>
+      </c>
+      <c r="C50" s="6">
+        <v>0</v>
+      </c>
+      <c r="D50" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="E50" s="6" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" s="5" t="s">
+        <v>415</v>
+      </c>
+      <c r="C51" s="5">
+        <v>1</v>
+      </c>
+      <c r="D51" s="5" t="s">
+        <v>333</v>
+      </c>
+      <c r="E51" s="5" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" s="6" t="s">
+        <v>415</v>
+      </c>
+      <c r="C52" s="6">
+        <v>2</v>
+      </c>
+      <c r="D52" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="E52" s="6" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" s="5" t="s">
+        <v>418</v>
+      </c>
+      <c r="C53" s="5">
+        <v>0</v>
+      </c>
+      <c r="D53" s="5" t="s">
+        <v>333</v>
+      </c>
+      <c r="E53" s="5" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" s="6" t="s">
+        <v>418</v>
+      </c>
+      <c r="C54" s="6">
+        <v>1</v>
+      </c>
+      <c r="D54" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="E54" s="6" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" s="5" t="s">
+        <v>418</v>
+      </c>
+      <c r="C55" s="5">
+        <v>2</v>
+      </c>
+      <c r="D55" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="E55" s="5" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" s="6" t="s">
+        <v>424</v>
+      </c>
+      <c r="C56" s="6">
+        <v>0</v>
+      </c>
+      <c r="D56" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="E56" s="6" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" s="5" t="s">
+        <v>424</v>
+      </c>
+      <c r="C57" s="5">
+        <v>1</v>
+      </c>
+      <c r="D57" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="E57" s="5" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="B58" s="6" t="s">
+        <v>424</v>
+      </c>
+      <c r="C58" s="6">
+        <v>2</v>
+      </c>
+      <c r="D58" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="E58" s="6" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59" s="5" t="s">
+        <v>424</v>
+      </c>
+      <c r="C59" s="5">
+        <v>3</v>
+      </c>
+      <c r="D59" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="E59" s="5" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" s="6" t="s">
+        <v>424</v>
+      </c>
+      <c r="C60" s="6">
+        <v>4</v>
+      </c>
+      <c r="D60" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="E60" s="6" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="B61" s="5" t="s">
+        <v>424</v>
+      </c>
+      <c r="C61" s="5">
+        <v>5</v>
+      </c>
+      <c r="D61" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="E61" s="5" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62" s="6" t="s">
+        <v>424</v>
+      </c>
+      <c r="C62" s="6">
+        <v>6</v>
+      </c>
+      <c r="D62" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="E62" s="6" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" s="5" t="s">
+        <v>424</v>
+      </c>
+      <c r="C63" s="5">
+        <v>7</v>
+      </c>
+      <c r="D63" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="E63" s="5" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="B64" s="6" t="s">
+        <v>424</v>
+      </c>
+      <c r="C64" s="6">
+        <v>8</v>
+      </c>
+      <c r="D64" s="6" t="s">
+        <v>506</v>
+      </c>
+      <c r="E64" s="6" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="B65" s="5" t="s">
+        <v>424</v>
+      </c>
+      <c r="C65" s="5">
+        <v>9</v>
+      </c>
+      <c r="D65" s="5" t="s">
+        <v>506</v>
+      </c>
+      <c r="E65" s="5" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="B66" s="6" t="s">
+        <v>424</v>
+      </c>
+      <c r="C66" s="6">
+        <v>10</v>
+      </c>
+      <c r="D66" s="6" t="s">
+        <v>506</v>
+      </c>
+      <c r="E66" s="6" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="B67" s="5" t="s">
+        <v>424</v>
+      </c>
+      <c r="C67" s="5">
+        <v>11</v>
+      </c>
+      <c r="D67" s="5" t="s">
+        <v>506</v>
+      </c>
+      <c r="E67" s="5" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="B68" s="6" t="s">
+        <v>424</v>
+      </c>
+      <c r="C68" s="6">
+        <v>12</v>
+      </c>
+      <c r="D68" s="6" t="s">
+        <v>506</v>
+      </c>
+      <c r="E68" s="6" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69" s="5" t="s">
+        <v>424</v>
+      </c>
+      <c r="C69" s="5">
+        <v>13</v>
+      </c>
+      <c r="D69" s="5" t="s">
+        <v>506</v>
+      </c>
+      <c r="E69" s="5" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="B70" s="6" t="s">
+        <v>424</v>
+      </c>
+      <c r="C70" s="6">
+        <v>14</v>
+      </c>
+      <c r="D70" s="6" t="s">
+        <v>506</v>
+      </c>
+      <c r="E70" s="6" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="B71" s="5" t="s">
+        <v>424</v>
+      </c>
+      <c r="C71" s="5">
+        <v>15</v>
+      </c>
+      <c r="D71" s="5" t="s">
+        <v>506</v>
+      </c>
+      <c r="E71" s="5" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="B72" s="6" t="s">
+        <v>424</v>
+      </c>
+      <c r="C72" s="6">
+        <v>16</v>
+      </c>
+      <c r="D72" s="6" t="s">
+        <v>477</v>
+      </c>
+      <c r="E72" s="6" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="B73" s="5" t="s">
+        <v>424</v>
+      </c>
+      <c r="C73" s="5">
+        <v>17</v>
+      </c>
+      <c r="D73" s="5" t="s">
+        <v>477</v>
+      </c>
+      <c r="E73" s="5" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="B74" s="6" t="s">
+        <v>424</v>
+      </c>
+      <c r="C74" s="6">
+        <v>18</v>
+      </c>
+      <c r="D74" s="6" t="s">
+        <v>477</v>
+      </c>
+      <c r="E74" s="6" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="B75" s="5" t="s">
+        <v>424</v>
+      </c>
+      <c r="C75" s="5">
+        <v>19</v>
+      </c>
+      <c r="D75" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="E75" s="5" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="B76" s="6" t="s">
+        <v>424</v>
+      </c>
+      <c r="C76" s="6">
+        <v>20</v>
+      </c>
+      <c r="D76" s="6" t="s">
+        <v>345</v>
+      </c>
+      <c r="E76" s="6" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="B77" s="5" t="s">
+        <v>424</v>
+      </c>
+      <c r="C77" s="5">
+        <v>21</v>
+      </c>
+      <c r="D77" s="5" t="s">
+        <v>345</v>
+      </c>
+      <c r="E77" s="5" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="B78" s="6" t="s">
+        <v>424</v>
+      </c>
+      <c r="C78" s="6">
+        <v>22</v>
+      </c>
+      <c r="D78" s="6" t="s">
+        <v>345</v>
+      </c>
+      <c r="E78" s="6" t="s">
+        <v>349</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="B2:E78"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1:I11"/>
+  <sheetFormatPr defaultColWidth="8.43" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="48.046875" customWidth="1"/>
+    <col min="2" max="2" width="53.90625" customWidth="1"/>
+    <col min="3" max="3" width="24.609375" customWidth="1"/>
+    <col min="4" max="4" width="53.90625" customWidth="1"/>
+    <col min="5" max="5" width="19.921875" customWidth="1"/>
+    <col min="6" max="6" width="23.4375" customWidth="1"/>
+    <col min="7" max="7" width="19.921875" customWidth="1"/>
+    <col min="8" max="8" width="11.71875" customWidth="1"/>
+    <col min="9" max="9" width="15.234375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>524</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>525</v>
+      </c>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>526</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>527</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>528</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>429</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>530</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>531</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>532</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>534</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>535</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>536</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>537</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>538</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>539</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="5" t="s">
+        <v>374</v>
+      </c>
+      <c r="C5" s="5">
+        <v>0</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>541</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="F5" s="5">
+        <v>1</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="6" t="s">
+        <v>374</v>
+      </c>
+      <c r="C6" s="6">
+        <v>1</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>543</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="F6" s="6">
+        <v>2</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>252</v>
+      </c>
+      <c r="H6" s="6" t="s">
+        <v>252</v>
+      </c>
+      <c r="I6" s="6" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="5" t="s">
+        <v>382</v>
+      </c>
+      <c r="C7" s="5">
+        <v>0</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>544</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="F7" s="5">
+        <v>1</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="I7" s="5" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="6" t="s">
+        <v>391</v>
+      </c>
+      <c r="C8" s="6">
+        <v>0</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>545</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="F8" s="6">
+        <v>1</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>252</v>
+      </c>
+      <c r="H8" s="6" t="s">
+        <v>252</v>
+      </c>
+      <c r="I8" s="6" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="5" t="s">
+        <v>391</v>
+      </c>
+      <c r="C9" s="5">
+        <v>1</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>543</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="F9" s="5">
+        <v>1</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>546</v>
+      </c>
+      <c r="H9" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="I9" s="5" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="6" t="s">
+        <v>394</v>
+      </c>
+      <c r="C10" s="6">
+        <v>0</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>547</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="F10" s="6">
+        <v>1</v>
+      </c>
+      <c r="G10" s="6" t="s">
+        <v>252</v>
+      </c>
+      <c r="H10" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="I10" s="6" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="5" t="s">
+        <v>406</v>
+      </c>
+      <c r="C11" s="5">
+        <v>0</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>547</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="F11" s="5">
+        <v>1</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>548</v>
+      </c>
+      <c r="H11" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="I11" s="5" t="s">
+        <v>542</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="B2:I11"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>